--- a/output/yearly_surface_area_iteration_49_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_49_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449762985668</v>
+        <v>10.84497619106944</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907182466292</v>
+        <v>37.78907145009082</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.956664232292898</v>
+        <v>6.794675861092174</v>
       </c>
       <c r="C2" t="n">
-        <v>5.791329707351935</v>
+        <v>5.482079180514189</v>
       </c>
       <c r="D2" t="n">
-        <v>27.31811161837174</v>
+        <v>19.53677931451153</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.04514469886213</v>
+        <v>20.12091919853838</v>
       </c>
       <c r="C3" t="n">
-        <v>32.40749171718721</v>
+        <v>25.81505588316988</v>
       </c>
       <c r="D3" t="n">
-        <v>61.30523539169208</v>
+        <v>62.30170931150259</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.38874069981528</v>
+        <v>37.48410909584747</v>
       </c>
       <c r="C4" t="n">
-        <v>86.49295449184824</v>
+        <v>75.08308267309181</v>
       </c>
       <c r="D4" t="n">
-        <v>80.32856065688252</v>
+        <v>85.12734343524093</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.55433726666352</v>
+        <v>47.49204519293946</v>
       </c>
       <c r="C5" t="n">
-        <v>122.1048707156971</v>
+        <v>103.5498391054324</v>
       </c>
       <c r="D5" t="n">
-        <v>59.22393025868885</v>
+        <v>62.36552291227864</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.58374864006191</v>
+        <v>43.99505987041232</v>
       </c>
       <c r="C6" t="n">
-        <v>128.6845438295592</v>
+        <v>89.11716610529999</v>
       </c>
       <c r="D6" t="n">
-        <v>42.22398701195107</v>
+        <v>44.31707311740527</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.95570784678443</v>
+        <v>29.76364514965055</v>
       </c>
       <c r="C7" t="n">
-        <v>111.1495480840069</v>
+        <v>76.83452057746811</v>
       </c>
       <c r="D7" t="n">
-        <v>38.0279973240002</v>
+        <v>38.86640986342697</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.19040230136165</v>
+        <v>15.85522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>74.18576527141022</v>
+        <v>51.57120690408495</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.209374302911826</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>44.70780870369548</v>
+        <v>35.61093447614454</v>
       </c>
       <c r="D9" t="n">
         <v>33.9468721174462</v>
@@ -895,10 +895,10 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
         <v>34.93156506480576</v>
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.679419443151373</v>
+        <v>7.718850107859557</v>
       </c>
       <c r="C21" t="n">
-        <v>93.1129607482104</v>
+        <v>96.48562634824448</v>
       </c>
       <c r="D21" t="n">
-        <v>8.639346873545295</v>
+        <v>8.683706371342002</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.397468951499716</v>
+        <v>8.829838851995813</v>
       </c>
       <c r="C2" t="n">
-        <v>5.994551482131024</v>
+        <v>7.587928006123597</v>
       </c>
       <c r="D2" t="n">
-        <v>26.17732078603695</v>
+        <v>22.19044335909065</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.48693116577319</v>
+        <v>21.45609607631404</v>
       </c>
       <c r="C3" t="n">
-        <v>27.21404636172158</v>
+        <v>23.29687302177681</v>
       </c>
       <c r="D3" t="n">
-        <v>67.42152358914971</v>
+        <v>63.10674242898497</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.08694324398402</v>
+        <v>37.68831261833081</v>
       </c>
       <c r="C4" t="n">
-        <v>83.63410517708152</v>
+        <v>69.54406212573132</v>
       </c>
       <c r="D4" t="n">
-        <v>90.7812284639983</v>
+        <v>95.80974020515048</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.02758071783948</v>
+        <v>52.10625940289948</v>
       </c>
       <c r="C5" t="n">
-        <v>138.3282515283756</v>
+        <v>119.9941131515664</v>
       </c>
       <c r="D5" t="n">
-        <v>71.47123286916781</v>
+        <v>76.40451508300804</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.08943082320704</v>
+        <v>53.5749539684527</v>
       </c>
       <c r="C6" t="n">
-        <v>157.7864910265474</v>
+        <v>126.1486895094897</v>
       </c>
       <c r="D6" t="n">
-        <v>50.07305990740432</v>
+        <v>53.17243740971151</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.73529763941441</v>
+        <v>40.60312155223958</v>
       </c>
       <c r="C7" t="n">
-        <v>146.4826479598496</v>
+        <v>101.6874637104761</v>
       </c>
       <c r="D7" t="n">
-        <v>40.90255460203486</v>
+        <v>42.69915290080652</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.20284622634736</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="C8" t="n">
-        <v>107.3982901060798</v>
+        <v>76.52232480751763</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.46978379091126</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.20312396378785</v>
+        <v>11.6484365108884</v>
       </c>
       <c r="C9" t="n">
-        <v>66.78436932909349</v>
+        <v>49.36718330805084</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>41.28249096357838</v>
+        <v>36.86953503298896</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
         <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>28.61794557879453</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.855504751682256</v>
+        <v>7.907666990962406</v>
       </c>
       <c r="C21" t="n">
-        <v>101.139623677909</v>
+        <v>105.7650460041222</v>
       </c>
       <c r="D21" t="n">
-        <v>9.819380939602819</v>
+        <v>9.884583738703007</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.022842239104934</v>
+        <v>9.318749208710724</v>
       </c>
       <c r="C2" t="n">
-        <v>6.888923640699868</v>
+        <v>10.94452340694344</v>
       </c>
       <c r="D2" t="n">
-        <v>21.73883941513712</v>
+        <v>28.51191682673587</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.01707492606647</v>
+        <v>25.27509464583413</v>
       </c>
       <c r="C3" t="n">
-        <v>25.41744806294992</v>
+        <v>26.11448893296516</v>
       </c>
       <c r="D3" t="n">
-        <v>70.72019587541898</v>
+        <v>65.08987279156354</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.91277298970483</v>
+        <v>38.44131310748811</v>
       </c>
       <c r="C4" t="n">
-        <v>75.64464235992098</v>
+        <v>63.37966829076559</v>
       </c>
       <c r="D4" t="n">
-        <v>99.31948824783282</v>
+        <v>102.4591174060141</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.84381397069608</v>
+        <v>53.77523050011905</v>
       </c>
       <c r="C5" t="n">
-        <v>143.4087958978529</v>
+        <v>122.3993950269711</v>
       </c>
       <c r="D5" t="n">
-        <v>84.13577825395166</v>
+        <v>90.63985679458678</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.34102027740147</v>
+        <v>60.86050368166828</v>
       </c>
       <c r="C6" t="n">
-        <v>184.2318289358437</v>
+        <v>155.4518949858485</v>
       </c>
       <c r="D6" t="n">
-        <v>57.92213280285758</v>
+        <v>62.30956329313658</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>55.69454726192155</v>
+        <v>50.84373185523806</v>
       </c>
       <c r="C7" t="n">
-        <v>179.5400566572482</v>
+        <v>136.8409037564417</v>
       </c>
       <c r="D7" t="n">
-        <v>45.09461729916874</v>
+        <v>47.60985491744906</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>35.13184159647211</v>
+        <v>33.04562772494764</v>
       </c>
       <c r="C8" t="n">
-        <v>143.1977201414398</v>
+        <v>103.3093109178918</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>40.55599766243574</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.86093598336221</v>
+        <v>16.9734360587231</v>
       </c>
       <c r="C9" t="n">
-        <v>94.96249193638545</v>
+        <v>69.33593161243097</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>37.38593432542277</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.683558444063038</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>56.51430659496764</v>
+        <v>46.83427423109409</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.686282702997524</v>
       </c>
       <c r="C11" t="n">
-        <v>38.91549724863931</v>
+        <v>37.31623023842126</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>31.47974013667398</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.82120841130262</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.015471253276919</v>
+        <v>8.08090250838478</v>
       </c>
       <c r="C21" t="n">
-        <v>109.210795825898</v>
+        <v>114.142747930935</v>
       </c>
       <c r="D21" t="n">
-        <v>11.02127297325576</v>
+        <v>11.11124094902907</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.448519832120549</v>
+        <v>8.498989875664638</v>
       </c>
       <c r="C2" t="n">
-        <v>4.738896168399354</v>
+        <v>7.266896506834891</v>
       </c>
       <c r="D2" t="n">
-        <v>18.06906649666254</v>
+        <v>23.08088852684251</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.24488145118073</v>
+        <v>28.96155727528091</v>
       </c>
       <c r="C3" t="n">
-        <v>40.26638208968293</v>
+        <v>42.10225029662447</v>
       </c>
       <c r="D3" t="n">
-        <v>76.2278004962436</v>
+        <v>72.85058839363457</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.22662915542755</v>
+        <v>25.83174559414208</v>
       </c>
       <c r="C4" t="n">
-        <v>112.9755988139059</v>
+        <v>96.99667317958487</v>
       </c>
       <c r="D4" t="n">
-        <v>95.06950243614838</v>
+        <v>99.98314969590368</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.92000507653306</v>
+        <v>34.28753857081986</v>
       </c>
       <c r="C5" t="n">
-        <v>110.0784613386736</v>
+        <v>92.87333282174828</v>
       </c>
       <c r="D5" t="n">
-        <v>57.21134746498289</v>
+        <v>62.46369768270332</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.57617239586842</v>
+        <v>31.55729820530948</v>
       </c>
       <c r="C6" t="n">
-        <v>118.2593649581623</v>
+        <v>90.12345750215297</v>
       </c>
       <c r="D6" t="n">
-        <v>29.66547037922588</v>
+        <v>31.35603992593888</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.29589127407256</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="C7" t="n">
-        <v>100.6693913411722</v>
+        <v>72.64245788033423</v>
       </c>
       <c r="D7" t="n">
-        <v>27.78738702100172</v>
+        <v>28.50602634051038</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.35038611942487</v>
+        <v>11.76624623539802</v>
       </c>
       <c r="C8" t="n">
-        <v>69.9298889735003</v>
+        <v>51.07051557491908</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>43.15468383557703</v>
+        <v>35.72187196672443</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.611268966847269</v>
+        <v>4.956844158742146</v>
       </c>
       <c r="C2" t="n">
-        <v>2.690970457340507</v>
+        <v>3.204424506661589</v>
       </c>
       <c r="D2" t="n">
-        <v>12.73621296719387</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.79818624574844</v>
+        <v>30.06602344255857</v>
       </c>
       <c r="C3" t="n">
-        <v>29.76659039276329</v>
+        <v>35.61289797155305</v>
       </c>
       <c r="D3" t="n">
-        <v>74.4851983212055</v>
+        <v>75.3638625165064</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.94731408580271</v>
+        <v>39.37299167881833</v>
       </c>
       <c r="C4" t="n">
-        <v>110.0529358983632</v>
+        <v>104.6798307130204</v>
       </c>
       <c r="D4" t="n">
-        <v>107.9343243525986</v>
+        <v>111.6355131976091</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.43604451606839</v>
+        <v>37.92000507653306</v>
       </c>
       <c r="C5" t="n">
-        <v>157.3005259129452</v>
+        <v>134.057649014902</v>
       </c>
       <c r="D5" t="n">
-        <v>72.23208733995908</v>
+        <v>79.79154466265952</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.97618567985338</v>
+        <v>38.27932473628739</v>
       </c>
       <c r="C6" t="n">
-        <v>146.9587955964093</v>
+        <v>118.2593649581623</v>
       </c>
       <c r="D6" t="n">
-        <v>36.30699359845555</v>
+        <v>38.68184129502858</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.91849924501429</v>
+        <v>20.66088043587412</v>
       </c>
       <c r="C7" t="n">
-        <v>128.3968917522148</v>
+        <v>96.47732864403831</v>
       </c>
       <c r="D7" t="n">
-        <v>30.30262463928205</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>9.930378028456486</v>
       </c>
       <c r="C8" t="n">
-        <v>92.37755023110363</v>
+        <v>66.92574099850506</v>
       </c>
       <c r="D8" t="n">
-        <v>28.12216298814988</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>48.14687091167205</v>
+        <v>42.15624642035802</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
         <v>30.03657101143117</v>
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.093708000259952</v>
+        <v>4.787001805907448</v>
       </c>
       <c r="C2" t="n">
-        <v>10.46739402267949</v>
+        <v>5.139449231732052</v>
       </c>
       <c r="D2" t="n">
-        <v>19.56426825023044</v>
+        <v>25.3016018338488</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.90279128174634</v>
+        <v>23.32141671438298</v>
       </c>
       <c r="C3" t="n">
-        <v>19.59568417676634</v>
+        <v>22.85999529338698</v>
       </c>
       <c r="D3" t="n">
-        <v>68.00566347317655</v>
+        <v>70.96563280148068</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.99684343937156</v>
+        <v>48.76635371305181</v>
       </c>
       <c r="C4" t="n">
-        <v>91.76395791594936</v>
+        <v>96.34577445166923</v>
       </c>
       <c r="D4" t="n">
-        <v>118.6422465628185</v>
+        <v>122.8028933334165</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.60909415392309</v>
+        <v>47.86020058203201</v>
       </c>
       <c r="C5" t="n">
-        <v>181.0833640483242</v>
+        <v>165.4735755507999</v>
       </c>
       <c r="D5" t="n">
-        <v>90.81166264282997</v>
+        <v>99.37741136238341</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.86551023118075</v>
+        <v>44.59883470852411</v>
       </c>
       <c r="C6" t="n">
-        <v>194.5362528396182</v>
+        <v>163.8644910635394</v>
       </c>
       <c r="D6" t="n">
-        <v>47.61770889908305</v>
+        <v>52.28690098048088</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.39865598784899</v>
+        <v>31.20092378866788</v>
       </c>
       <c r="C7" t="n">
-        <v>168.4610338148229</v>
+        <v>133.1878205489393</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>34.49468733641593</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.27108553955913</v>
+        <v>14.77039421039326</v>
       </c>
       <c r="C8" t="n">
-        <v>128.0100831567416</v>
+        <v>95.9658380901257</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>30.70906818884022</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>76.32499351896399</v>
+        <v>61.23749480009903</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>43.41779222031519</v>
+        <v>40.28601704376787</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>20.28094407433061</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.609886308515522</v>
+        <v>2.835287369864788</v>
       </c>
       <c r="C2" t="n">
-        <v>4.876340846993907</v>
+        <v>2.327723806769188</v>
       </c>
       <c r="D2" t="n">
-        <v>13.65316532296039</v>
+        <v>17.44271146135308</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.30178176029805</v>
+        <v>22.62928458288898</v>
       </c>
       <c r="C3" t="n">
-        <v>29.99730110326129</v>
+        <v>23.08579726536375</v>
       </c>
       <c r="D3" t="n">
-        <v>69.5813685384927</v>
+        <v>75.48167224101601</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.34893101229767</v>
+        <v>53.66723825265188</v>
       </c>
       <c r="C4" t="n">
-        <v>85.33154695772427</v>
+        <v>91.75119519579417</v>
       </c>
       <c r="D4" t="n">
-        <v>126.197776894702</v>
+        <v>130.8816951916635</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.81802648847841</v>
+        <v>49.62734644967627</v>
       </c>
       <c r="C5" t="n">
-        <v>209.3822416232385</v>
+        <v>192.5452684954057</v>
       </c>
       <c r="D5" t="n">
-        <v>95.9903817827319</v>
+        <v>107.5750046928443</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.9698942830004</v>
+        <v>37.91705983342032</v>
       </c>
       <c r="C6" t="n">
-        <v>230.0784649764655</v>
+        <v>199.5677098238831</v>
       </c>
       <c r="D6" t="n">
-        <v>46.97368240509714</v>
+        <v>51.56237117474674</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.12083708308037</v>
+        <v>9.761517423326035</v>
       </c>
       <c r="C7" t="n">
-        <v>172.7129831219159</v>
+        <v>135.2239652875472</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>95.13135254151592</v>
+        <v>76.10508203321274</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>33.05937219280708</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.7904711328347</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.543528375254239</v>
+        <v>3.848451000647497</v>
       </c>
       <c r="C2" t="n">
-        <v>4.648575379608647</v>
+        <v>3.033600406122644</v>
       </c>
       <c r="D2" t="n">
-        <v>11.78293594637022</v>
+        <v>12.96005144376214</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.02979658849267</v>
+        <v>16.33137306014569</v>
       </c>
       <c r="C3" t="n">
-        <v>24.43570035870311</v>
+        <v>15.60487975900305</v>
       </c>
       <c r="D3" t="n">
-        <v>65.39421457988004</v>
+        <v>72.00137662946108</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.57942073861742</v>
+        <v>48.85569275413827</v>
       </c>
       <c r="C4" t="n">
-        <v>80.09883169408876</v>
+        <v>75.18518443433348</v>
       </c>
       <c r="D4" t="n">
-        <v>130.7540679901115</v>
+        <v>137.5693605529928</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.88094045700822</v>
+        <v>63.24909584610077</v>
       </c>
       <c r="C5" t="n">
-        <v>186.5811511921063</v>
+        <v>182.9486846863931</v>
       </c>
       <c r="D5" t="n">
-        <v>114.1772580039041</v>
+        <v>126.424560614383</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.56866257159972</v>
+        <v>50.03280825153021</v>
       </c>
       <c r="C6" t="n">
-        <v>280.3125315073664</v>
+        <v>249.8420280106581</v>
       </c>
       <c r="D6" t="n">
-        <v>61.18251692866124</v>
+        <v>69.35360307110744</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.21793229480956</v>
+        <v>21.61906619521901</v>
       </c>
       <c r="C7" t="n">
-        <v>240.8040586453619</v>
+        <v>204.3331131802971</v>
       </c>
       <c r="D7" t="n">
-        <v>38.14777054391831</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>149.7067074205961</v>
+        <v>119.3314334511998</v>
       </c>
       <c r="D8" t="n">
-        <v>32.87873061522568</v>
+        <v>34.21390749300134</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>64.12186955517615</v>
+        <v>55.02499532762521</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.151410130632261</v>
+        <v>3.003166227290993</v>
       </c>
       <c r="C2" t="n">
-        <v>2.981567777797563</v>
+        <v>2.421971586376881</v>
       </c>
       <c r="D2" t="n">
-        <v>9.365873098514571</v>
+        <v>9.203884727313847</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.11186248502191</v>
+        <v>15.13854959948582</v>
       </c>
       <c r="C3" t="n">
-        <v>21.97151362104362</v>
+        <v>14.11753198706914</v>
       </c>
       <c r="D3" t="n">
-        <v>61.05488972710914</v>
+        <v>67.22026530977911</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.59745205019236</v>
+        <v>42.84445156103505</v>
       </c>
       <c r="C4" t="n">
-        <v>74.04930234051992</v>
+        <v>60.77607337910305</v>
       </c>
       <c r="D4" t="n">
-        <v>134.5573585963636</v>
+        <v>141.372651159245</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67.69150420781759</v>
+        <v>69.45865007546185</v>
       </c>
       <c r="C5" t="n">
-        <v>176.4936935309703</v>
+        <v>171.8058482431918</v>
       </c>
       <c r="D5" t="n">
-        <v>126.277298458746</v>
+        <v>140.9053392520235</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.02780170201773</v>
+        <v>60.09572222006002</v>
       </c>
       <c r="C6" t="n">
-        <v>299.9955912298107</v>
+        <v>276.2068626082062</v>
       </c>
       <c r="D6" t="n">
-        <v>73.13725872327464</v>
+        <v>81.79136473621028</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.00212772632452</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="C7" t="n">
-        <v>300.391235554622</v>
+        <v>260.8660729816455</v>
       </c>
       <c r="D7" t="n">
-        <v>42.16017341117502</v>
+        <v>44.79518424937346</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>194.3516842712198</v>
+        <v>158.9694970101648</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>74.66093116026566</v>
+        <v>66.11874438561416</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.522911673465055</v>
+        <v>5.391758391723482</v>
       </c>
       <c r="C2" t="n">
-        <v>13.8966387536136</v>
+        <v>10.004009106275</v>
       </c>
       <c r="D2" t="n">
-        <v>16.8369731278328</v>
+        <v>12.2041057114921</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.99481352403828</v>
+        <v>12.68908907739002</v>
       </c>
       <c r="C3" t="n">
-        <v>17.05786636128833</v>
+        <v>11.90859965251381</v>
       </c>
       <c r="D3" t="n">
-        <v>55.43929285881739</v>
+        <v>60.74073046175016</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.53065214857457</v>
+        <v>36.13126075939537</v>
       </c>
       <c r="C4" t="n">
-        <v>65.35788991482291</v>
+        <v>48.52386203010285</v>
       </c>
       <c r="D4" t="n">
-        <v>133.9447480289136</v>
+        <v>140.517548908846</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>66.70975650357077</v>
+        <v>68.20692175254716</v>
       </c>
       <c r="C5" t="n">
-        <v>159.0676717805895</v>
+        <v>146.6731070144735</v>
       </c>
       <c r="D5" t="n">
-        <v>140.2426595516569</v>
+        <v>155.4597489674825</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>73.05675541152641</v>
+        <v>73.09700706740053</v>
       </c>
       <c r="C6" t="n">
-        <v>293.3943196664551</v>
+        <v>276.0056043288356</v>
       </c>
       <c r="D6" t="n">
-        <v>88.91590782592939</v>
+        <v>100.7901463087946</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.72856427420492</v>
+        <v>37.84833749412304</v>
       </c>
       <c r="C7" t="n">
-        <v>354.5886175675672</v>
+        <v>318.1176721025025</v>
       </c>
       <c r="D7" t="n">
-        <v>49.52622643613884</v>
+        <v>54.07760879302705</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>275.2133339315083</v>
+        <v>234.5738877142116</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>38.80357801035517</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>134.6781135639859</v>
+        <v>114.3765527878661</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>34.50155957034565</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>51.10487674456772</v>
+        <v>49.68134257340984</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>27.18950266911542</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
         <v>24.52209415667683</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.98419422574081</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.67690719431156</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.197192419833367</v>
+        <v>5.578290455530377</v>
       </c>
       <c r="C2" t="n">
-        <v>8.838674581334034</v>
+        <v>4.723188205131405</v>
       </c>
       <c r="D2" t="n">
-        <v>3.013965452037707</v>
+        <v>6.117269945161876</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.273146845958866</v>
+        <v>3.814089830998858</v>
       </c>
       <c r="C2" t="n">
-        <v>8.004189032724245</v>
+        <v>5.6018524004323</v>
       </c>
       <c r="D2" t="n">
-        <v>12.52611895848505</v>
+        <v>8.982009746154068</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.53048791765854</v>
+        <v>17.77945092390974</v>
       </c>
       <c r="C3" t="n">
-        <v>30.3016428915778</v>
+        <v>22.06477965294707</v>
       </c>
       <c r="D3" t="n">
-        <v>61.39359268507428</v>
+        <v>65.84581852383357</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.75283022937061</v>
+        <v>50.8466770983508</v>
       </c>
       <c r="C4" t="n">
-        <v>93.19338257333273</v>
+        <v>72.8368439257751</v>
       </c>
       <c r="D4" t="n">
-        <v>137.0843771870949</v>
+        <v>144.0783478321491</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.38695713085605</v>
+        <v>43.68777283898307</v>
       </c>
       <c r="C5" t="n">
-        <v>244.3079162018188</v>
+        <v>227.4463993813798</v>
       </c>
       <c r="D5" t="n">
-        <v>127.5290267816607</v>
+        <v>143.5315143608837</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.42646371873739</v>
+        <v>23.46671537461151</v>
       </c>
       <c r="C6" t="n">
-        <v>288.1616044028196</v>
+        <v>266.3049552631728</v>
       </c>
       <c r="D6" t="n">
-        <v>71.92970904705108</v>
+        <v>80.34230512474198</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.647413705455153</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>193.5535233876672</v>
+        <v>164.9277238272387</v>
       </c>
       <c r="D7" t="n">
-        <v>31.68001666834032</v>
+        <v>34.13536767666159</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>99.22033172970389</v>
+        <v>84.28304040958866</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>25.36836067773758</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>38.93905919354123</v>
+        <v>37.94062177832222</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D10" t="n">
         <v>19.21771131063132</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.8811517745239</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>9.886199381765381</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.626036240139976</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.267878254539137</v>
+        <v>6.154576357923254</v>
       </c>
       <c r="C2" t="n">
-        <v>4.532729150507524</v>
+        <v>3.238785676310227</v>
       </c>
       <c r="D2" t="n">
-        <v>13.04546349403162</v>
+        <v>15.17585601224719</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.28090301660161</v>
+        <v>11.849694790259</v>
       </c>
       <c r="C3" t="n">
-        <v>22.2709466708389</v>
+        <v>12.09022297779947</v>
       </c>
       <c r="D3" t="n">
-        <v>5.66959299202533</v>
+        <v>8.51666133434108</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39873216728436</v>
+        <v>13.39918489694889</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14630369931224</v>
+        <v>70.14867387226182</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576321431445219</v>
+        <v>1.576374693758692</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.301437602932777</v>
+        <v>4.543528375254239</v>
       </c>
       <c r="C2" t="n">
-        <v>4.420809912223387</v>
+        <v>3.240749171718721</v>
       </c>
       <c r="D2" t="n">
-        <v>21.31276091149401</v>
+        <v>13.003248342749</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.2057504117311</v>
+        <v>17.49965282819939</v>
       </c>
       <c r="C3" t="n">
-        <v>19.39442589739574</v>
+        <v>12.43874341280709</v>
       </c>
       <c r="D3" t="n">
-        <v>15.25635932399543</v>
+        <v>19.20298509506761</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.68913013511903</v>
+        <v>13.80926320793563</v>
       </c>
       <c r="C4" t="n">
-        <v>34.45934441906305</v>
+        <v>19.25894471420968</v>
       </c>
       <c r="D4" t="n">
-        <v>18.04648629946487</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="5">
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
         <v>16.54343056426301</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44208857137163</v>
+        <v>15.44470620670441</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1505993981786</v>
+        <v>86.16520304792986</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250966015025607</v>
+        <v>3.251517096148297</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.046584110456105</v>
+        <v>5.891467973185108</v>
       </c>
       <c r="C2" t="n">
-        <v>10.26122700478766</v>
+        <v>7.215845626214056</v>
       </c>
       <c r="D2" t="n">
-        <v>21.95286041466293</v>
+        <v>25.8994861857351</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.60059291528757</v>
+        <v>16.53754007803752</v>
       </c>
       <c r="C3" t="n">
-        <v>18.06415775814131</v>
+        <v>12.55164439879547</v>
       </c>
       <c r="D3" t="n">
-        <v>28.76520773443155</v>
+        <v>25.14746744428205</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.00064725700153</v>
+        <v>25.49991487010665</v>
       </c>
       <c r="C4" t="n">
-        <v>42.78063796025901</v>
+        <v>26.39330528097125</v>
       </c>
       <c r="D4" t="n">
-        <v>21.64557338323367</v>
+        <v>24.58099901893164</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.14345833800705</v>
+        <v>12.34547738090364</v>
       </c>
       <c r="C5" t="n">
-        <v>38.58268477689965</v>
+        <v>22.89926520155685</v>
       </c>
       <c r="D5" t="n">
-        <v>28.96155727528091</v>
+        <v>29.82058651649687</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
         <v>36.6290068454485</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -5221,7 +5221,7 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D8" t="n">
         <v>38.55323234577224</v>
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.82369599052563</v>
       </c>
     </row>
     <row r="11">
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.735263575085</v>
+        <v>16.7448264121103</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0851078080185</v>
+        <v>102.1434411138728</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020579072525498</v>
+        <v>5.02344792363309</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.116689108085128</v>
+        <v>6.132977908429824</v>
       </c>
       <c r="C2" t="n">
-        <v>7.14417804380404</v>
+        <v>4.035964812158637</v>
       </c>
       <c r="D2" t="n">
-        <v>24.74004214701962</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.21418523044183</v>
+        <v>18.54030539470102</v>
       </c>
       <c r="C3" t="n">
-        <v>30.61089341841555</v>
+        <v>21.63281066307847</v>
       </c>
       <c r="D3" t="n">
-        <v>39.04901493641688</v>
+        <v>39.23554700022378</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.93156506480576</v>
+        <v>28.94584931201296</v>
       </c>
       <c r="C4" t="n">
-        <v>44.13348629671111</v>
+        <v>29.25215459573796</v>
       </c>
       <c r="D4" t="n">
-        <v>30.66881653296611</v>
+        <v>31.03893541746715</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.67961575771283</v>
+        <v>25.59907138823559</v>
       </c>
       <c r="C5" t="n">
-        <v>60.03387211469246</v>
+        <v>37.11006322052944</v>
       </c>
       <c r="D5" t="n">
-        <v>29.96784867213389</v>
+        <v>32.07860623626453</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.28304643845935</v>
+        <v>11.3107153006275</v>
       </c>
       <c r="C6" t="n">
-        <v>37.99756314516856</v>
+        <v>24.83527167433157</v>
       </c>
       <c r="D6" t="n">
-        <v>37.99756314516856</v>
+        <v>37.8768081775462</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.79389940203295</v>
       </c>
       <c r="D8" t="n">
         <v>40.38910055271378</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05985078338537</v>
+        <v>18.07944581291</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8190265392284</v>
+        <v>117.9468607794605</v>
       </c>
       <c r="D21" t="n">
-        <v>6.879943155575378</v>
+        <v>6.887407928727619</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.849072895453248</v>
+        <v>6.381360077604268</v>
       </c>
       <c r="C2" t="n">
-        <v>10.29067943591507</v>
+        <v>12.33173291304418</v>
       </c>
       <c r="D2" t="n">
-        <v>23.55114567717673</v>
+        <v>24.95799013736241</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.08164929036851</v>
+        <v>17.85308200172825</v>
       </c>
       <c r="C3" t="n">
-        <v>27.21404636172158</v>
+        <v>17.08731879241574</v>
       </c>
       <c r="D3" t="n">
-        <v>46.25504308558848</v>
+        <v>48.05164138436013</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.96762768795563</v>
+        <v>23.930100291016</v>
       </c>
       <c r="C4" t="n">
-        <v>52.16123727433728</v>
+        <v>36.41204060280995</v>
       </c>
       <c r="D4" t="n">
-        <v>37.2288546927433</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.69724615866027</v>
+        <v>21.52481841561132</v>
       </c>
       <c r="C5" t="n">
-        <v>52.76893910326607</v>
+        <v>34.23845118560752</v>
       </c>
       <c r="D5" t="n">
-        <v>27.34167356327368</v>
+        <v>29.28062527916113</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.89311267342412</v>
+        <v>12.67927160034756</v>
       </c>
       <c r="C6" t="n">
-        <v>46.12839763174064</v>
+        <v>29.22270216461057</v>
       </c>
       <c r="D6" t="n">
-        <v>30.3497485290859</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.108434215823654</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>24.55351008321272</v>
+        <v>18.44507586738907</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.06405994715006</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.057486821461419</v>
+        <v>7.070336564821941</v>
       </c>
       <c r="C21" t="n">
-        <v>66.16393895120081</v>
+        <v>67.16819736580844</v>
       </c>
       <c r="D21" t="n">
-        <v>5.293115116096065</v>
+        <v>5.302752423616456</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.683738370512286</v>
+        <v>5.254313713128929</v>
       </c>
       <c r="C2" t="n">
-        <v>10.0943298950657</v>
+        <v>6.695519342963247</v>
       </c>
       <c r="D2" t="n">
-        <v>21.53659938806228</v>
+        <v>18.40875120233194</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.68113728476482</v>
+        <v>20.77869016038374</v>
       </c>
       <c r="C3" t="n">
-        <v>35.59817175598934</v>
+        <v>37.80219535202343</v>
       </c>
       <c r="D3" t="n">
-        <v>54.86006171331176</v>
+        <v>57.94274950464675</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.82946330356409</v>
+        <v>31.14103717870883</v>
       </c>
       <c r="C4" t="n">
-        <v>62.32036251788328</v>
+        <v>40.64926369433918</v>
       </c>
       <c r="D4" t="n">
-        <v>52.46754255806228</v>
+        <v>54.67549314491337</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.63115026730624</v>
+        <v>30.11511082777092</v>
       </c>
       <c r="C5" t="n">
-        <v>79.49702035138549</v>
+        <v>55.14967728606459</v>
       </c>
       <c r="D5" t="n">
-        <v>35.41654843070369</v>
+        <v>36.66827675361837</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.20382797405162</v>
+        <v>22.58117894538089</v>
       </c>
       <c r="C6" t="n">
-        <v>67.98504677138737</v>
+        <v>44.59883470852411</v>
       </c>
       <c r="D6" t="n">
-        <v>32.68434456978482</v>
+        <v>33.52962934314132</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.81573453123786</v>
+        <v>11.25868267230242</v>
       </c>
       <c r="C7" t="n">
-        <v>49.58611304609789</v>
+        <v>32.87774886752143</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>33.77604801690726</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>27.03733177495716</v>
+        <v>22.5311098124643</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.51874800293658</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.279031717637533</v>
+        <v>7.298550174680632</v>
       </c>
       <c r="C21" t="n">
-        <v>75.51995407048942</v>
+        <v>77.54709560598172</v>
       </c>
       <c r="D21" t="n">
-        <v>6.369152752932841</v>
+        <v>6.386231402845554</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.047565858160352</v>
+        <v>6.005350706877739</v>
       </c>
       <c r="C2" t="n">
-        <v>7.283586217807087</v>
+        <v>5.775621744083985</v>
       </c>
       <c r="D2" t="n">
-        <v>20.24461940927348</v>
+        <v>21.19495118698439</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.82210804354885</v>
+        <v>19.56623174563893</v>
       </c>
       <c r="C3" t="n">
-        <v>37.76783418237479</v>
+        <v>30.48817495538469</v>
       </c>
       <c r="D3" t="n">
-        <v>59.36137493728339</v>
+        <v>59.40555358397449</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.51262083699963</v>
+        <v>36.53966780436203</v>
       </c>
       <c r="C4" t="n">
-        <v>77.25274509947727</v>
+        <v>73.55155625446679</v>
       </c>
       <c r="D4" t="n">
-        <v>68.17845106912399</v>
+        <v>72.3518605598772</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.08047192068179</v>
+        <v>39.73623832938966</v>
       </c>
       <c r="C5" t="n">
-        <v>99.91737259971916</v>
+        <v>67.02882450745099</v>
       </c>
       <c r="D5" t="n">
-        <v>45.92124886614456</v>
+        <v>48.69468613064181</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.6755498981756</v>
+        <v>32.68434456978482</v>
       </c>
       <c r="C6" t="n">
-        <v>100.1461198148086</v>
+        <v>69.15234479173684</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>37.55479493055324</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.57725195456389</v>
+        <v>20.06201433628357</v>
       </c>
       <c r="C7" t="n">
-        <v>76.29554108783661</v>
+        <v>50.90361846519711</v>
       </c>
       <c r="D7" t="n">
-        <v>35.15344004596554</v>
+        <v>36.4110588551057</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>47.73257338047992</v>
+        <v>34.38080460272329</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>26.73593522975338</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.486867701834075</v>
+        <v>7.515570335661844</v>
       </c>
       <c r="C21" t="n">
-        <v>84.22726164563335</v>
+        <v>87.36850515206893</v>
       </c>
       <c r="D21" t="n">
-        <v>7.486867701834075</v>
+        <v>7.515570335661844</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_49_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_49_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497619106944</v>
+        <v>10.84497655442673</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907145009082</v>
+        <v>37.78907271620098</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.794675861092174</v>
+        <v>4.89401230567035</v>
       </c>
       <c r="C2" t="n">
-        <v>5.482079180514189</v>
+        <v>9.410051745205678</v>
       </c>
       <c r="D2" t="n">
-        <v>19.53677931451153</v>
+        <v>30.67372527148734</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.12091919853838</v>
+        <v>16.93514789825748</v>
       </c>
       <c r="C3" t="n">
-        <v>25.81505588316988</v>
+        <v>34.65078522139117</v>
       </c>
       <c r="D3" t="n">
-        <v>62.30170931150259</v>
+        <v>73.00275928779283</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.48410909584747</v>
+        <v>33.68081848959532</v>
       </c>
       <c r="C4" t="n">
-        <v>75.08308267309181</v>
+        <v>98.70687768038282</v>
       </c>
       <c r="D4" t="n">
-        <v>85.12734343524093</v>
+        <v>104.5394407913131</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.49204519293946</v>
+        <v>40.47254910757476</v>
       </c>
       <c r="C5" t="n">
-        <v>103.5498391054324</v>
+        <v>130.5724446648258</v>
       </c>
       <c r="D5" t="n">
-        <v>62.36552291227864</v>
+        <v>79.74245727744719</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.99505987041232</v>
+        <v>35.26045054572845</v>
       </c>
       <c r="C6" t="n">
-        <v>89.11716610529999</v>
+        <v>104.2115370580947</v>
       </c>
       <c r="D6" t="n">
-        <v>44.31707311740527</v>
+        <v>52.97117913034091</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.76364514965055</v>
+        <v>24.19419042345839</v>
       </c>
       <c r="C7" t="n">
-        <v>76.83452057746811</v>
+        <v>72.16336500066178</v>
       </c>
       <c r="D7" t="n">
-        <v>38.86640986342697</v>
+        <v>40.78278138211675</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.85522542358599</v>
+        <v>12.51728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>51.57120690408495</v>
+        <v>41.22358610132356</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>35.61093447614454</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>28.75539025738908</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -912,7 +912,7 @@
         <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.20561154301086</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.718850107859557</v>
+        <v>7.706067559629497</v>
       </c>
       <c r="C21" t="n">
-        <v>96.48562634824448</v>
+        <v>96.32584449536873</v>
       </c>
       <c r="D21" t="n">
-        <v>8.683706371342002</v>
+        <v>8.669326004583185</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.829838851995813</v>
+        <v>6.188937527571892</v>
       </c>
       <c r="C2" t="n">
-        <v>7.587928006123597</v>
+        <v>7.394523708386976</v>
       </c>
       <c r="D2" t="n">
-        <v>22.19044335909065</v>
+        <v>25.64128653951819</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.45609607631404</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="C3" t="n">
-        <v>23.29687302177681</v>
+        <v>35.45090960035233</v>
       </c>
       <c r="D3" t="n">
-        <v>63.10674242898497</v>
+        <v>79.02578145334701</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.68831261833081</v>
+        <v>32.96610616090365</v>
       </c>
       <c r="C4" t="n">
-        <v>69.54406212573132</v>
+        <v>91.55975439346602</v>
       </c>
       <c r="D4" t="n">
-        <v>95.80974020515048</v>
+        <v>114.264633549582</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.10625940289948</v>
+        <v>44.86587008407924</v>
       </c>
       <c r="C5" t="n">
-        <v>119.9941131515664</v>
+        <v>155.7051858935442</v>
       </c>
       <c r="D5" t="n">
-        <v>76.40451508300804</v>
+        <v>97.09484795000957</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.5749539684527</v>
+        <v>44.11581483803468</v>
       </c>
       <c r="C6" t="n">
-        <v>126.1486895094897</v>
+        <v>151.7487426454295</v>
       </c>
       <c r="D6" t="n">
-        <v>53.17243740971151</v>
+        <v>64.20139111922018</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.60312155223958</v>
+        <v>32.69808903764427</v>
       </c>
       <c r="C7" t="n">
-        <v>101.6874637104761</v>
+        <v>109.4727230051533</v>
       </c>
       <c r="D7" t="n">
-        <v>42.69915290080652</v>
+        <v>45.51382356888213</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.86628669023996</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="C8" t="n">
-        <v>76.52232480751763</v>
+        <v>66.34160111447821</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.6484365108884</v>
+        <v>9.540624189870499</v>
       </c>
       <c r="C9" t="n">
-        <v>49.36718330805084</v>
+        <v>40.04843409934012</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>36.86953503298896</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.61794557879453</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.907666990962406</v>
+        <v>7.887631109935298</v>
       </c>
       <c r="C21" t="n">
-        <v>105.7650460041222</v>
+        <v>104.5111122066427</v>
       </c>
       <c r="D21" t="n">
-        <v>9.884583738703007</v>
+        <v>9.859538887419122</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.318749208710724</v>
+        <v>6.42062998577414</v>
       </c>
       <c r="C2" t="n">
-        <v>10.94452340694344</v>
+        <v>6.287112297996573</v>
       </c>
       <c r="D2" t="n">
-        <v>28.51191682673587</v>
+        <v>23.77007541522377</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.27509464583413</v>
+        <v>18.16724126708723</v>
       </c>
       <c r="C3" t="n">
-        <v>26.11448893296516</v>
+        <v>31.98043146583985</v>
       </c>
       <c r="D3" t="n">
-        <v>65.08987279156354</v>
+        <v>80.1351563591459</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.44131310748811</v>
+        <v>31.65154598491717</v>
       </c>
       <c r="C4" t="n">
-        <v>63.37966829076559</v>
+        <v>89.91336349344414</v>
       </c>
       <c r="D4" t="n">
-        <v>102.4591174060141</v>
+        <v>124.7938776776291</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.77523050011905</v>
+        <v>46.51029748869265</v>
       </c>
       <c r="C5" t="n">
-        <v>122.3993950269711</v>
+        <v>159.5585456327129</v>
       </c>
       <c r="D5" t="n">
-        <v>90.63985679458678</v>
+        <v>110.8638595020711</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.86050368166828</v>
+        <v>51.36111289537615</v>
       </c>
       <c r="C6" t="n">
-        <v>155.4518949858485</v>
+        <v>191.6381336166817</v>
       </c>
       <c r="D6" t="n">
-        <v>62.30956329313658</v>
+        <v>77.0014176871901</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>50.84373185523806</v>
+        <v>40.8426679920758</v>
       </c>
       <c r="C7" t="n">
-        <v>136.8409037564417</v>
+        <v>157.2622377524796</v>
       </c>
       <c r="D7" t="n">
-        <v>47.60985491744906</v>
+        <v>51.44259795482861</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.04562772494764</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="C8" t="n">
-        <v>103.3093109178918</v>
+        <v>99.38722883942584</v>
       </c>
       <c r="D8" t="n">
-        <v>40.55599766243574</v>
+        <v>41.80772598535042</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.9734360587231</v>
+        <v>13.42343636016663</v>
       </c>
       <c r="C9" t="n">
-        <v>69.33593161243097</v>
+        <v>58.3531200450219</v>
       </c>
       <c r="D9" t="n">
-        <v>37.38593432542277</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>46.83427423109409</v>
+        <v>38.72012945549421</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>37.31623023842126</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>37.31623023842126</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>31.47974013667398</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.44199175555609</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.08090250838478</v>
+        <v>8.052986985456828</v>
       </c>
       <c r="C21" t="n">
-        <v>114.142747930935</v>
+        <v>112.7418177963956</v>
       </c>
       <c r="D21" t="n">
-        <v>11.11124094902907</v>
+        <v>11.07285710500314</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.498989875664638</v>
+        <v>5.917975161199774</v>
       </c>
       <c r="C2" t="n">
-        <v>7.266896506834891</v>
+        <v>4.274529504290612</v>
       </c>
       <c r="D2" t="n">
-        <v>23.08088852684251</v>
+        <v>19.63102709411922</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.96155727528091</v>
+        <v>21.97642235956485</v>
       </c>
       <c r="C3" t="n">
-        <v>42.10225029662447</v>
+        <v>48.41488803493146</v>
       </c>
       <c r="D3" t="n">
-        <v>72.85058839363457</v>
+        <v>88.59291283123217</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.83174559414208</v>
+        <v>22.33476027161494</v>
       </c>
       <c r="C4" t="n">
-        <v>96.99667317958487</v>
+        <v>129.7075249373843</v>
       </c>
       <c r="D4" t="n">
-        <v>99.98314969590368</v>
+        <v>121.3096550752571</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.28753857081986</v>
+        <v>28.93701358267474</v>
       </c>
       <c r="C5" t="n">
-        <v>92.87333282174828</v>
+        <v>114.4963260077843</v>
       </c>
       <c r="D5" t="n">
-        <v>62.46369768270332</v>
+        <v>75.79092276785377</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.55729820530948</v>
+        <v>25.35854320069512</v>
       </c>
       <c r="C6" t="n">
-        <v>90.12345750215297</v>
+        <v>103.5675105641088</v>
       </c>
       <c r="D6" t="n">
-        <v>31.35603992593888</v>
+        <v>33.85164259013428</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.85861263505523</v>
+        <v>16.94791061841269</v>
       </c>
       <c r="C7" t="n">
-        <v>72.64245788033423</v>
+        <v>69.88767382221769</v>
       </c>
       <c r="D7" t="n">
-        <v>28.50602634051038</v>
+        <v>29.34443887993716</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.76624623539802</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>51.07051557491908</v>
+        <v>42.97600575340412</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>35.72187196672443</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.84531013555227</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.956844158742146</v>
+        <v>3.630503010304705</v>
       </c>
       <c r="C2" t="n">
-        <v>3.204424506661589</v>
+        <v>2.535854320069511</v>
       </c>
       <c r="D2" t="n">
-        <v>16.17036643664921</v>
+        <v>14.89998490735384</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.06602344255857</v>
+        <v>21.87333885061894</v>
       </c>
       <c r="C3" t="n">
-        <v>35.61289797155305</v>
+        <v>32.59402378099411</v>
       </c>
       <c r="D3" t="n">
-        <v>75.3638625165064</v>
+        <v>84.78864047727578</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.37299167881833</v>
+        <v>31.30695254072654</v>
       </c>
       <c r="C4" t="n">
-        <v>104.6798307130204</v>
+        <v>130.1797455831271</v>
       </c>
       <c r="D4" t="n">
-        <v>111.6355131976091</v>
+        <v>136.6887328622834</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.92000507653306</v>
+        <v>32.12769362147687</v>
       </c>
       <c r="C5" t="n">
-        <v>134.057649014902</v>
+        <v>173.3030134921682</v>
       </c>
       <c r="D5" t="n">
-        <v>79.79154466265952</v>
+        <v>94.59139130418019</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.27932473628739</v>
+        <v>30.71201343195298</v>
       </c>
       <c r="C6" t="n">
-        <v>118.2593649581623</v>
+        <v>137.9424246806066</v>
       </c>
       <c r="D6" t="n">
-        <v>38.68184129502858</v>
+        <v>43.1095234411817</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.66088043587412</v>
+        <v>15.92983824910874</v>
       </c>
       <c r="C7" t="n">
-        <v>96.47732864403831</v>
+        <v>99.11233948223673</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>32.15910954801276</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>66.92574099850506</v>
+        <v>58.16364273810228</v>
       </c>
       <c r="D8" t="n">
-        <v>28.78975142703771</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>42.15624642035802</v>
+        <v>34.83437204208531</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
         <v>30.03657101143117</v>
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.43093048890212</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.787001805907448</v>
+        <v>3.618722037853743</v>
       </c>
       <c r="C2" t="n">
-        <v>5.139449231732052</v>
+        <v>3.079742548222244</v>
       </c>
       <c r="D2" t="n">
-        <v>25.3016018338488</v>
+        <v>12.02935462013617</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.32141671438298</v>
+        <v>17.0529576227671</v>
       </c>
       <c r="C3" t="n">
-        <v>22.85999529338698</v>
+        <v>20.60197557361932</v>
       </c>
       <c r="D3" t="n">
-        <v>70.96563280148068</v>
+        <v>78.28456193664067</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.76635371305181</v>
+        <v>36.61624412529329</v>
       </c>
       <c r="C4" t="n">
-        <v>96.34577445166923</v>
+        <v>105.2158649595392</v>
       </c>
       <c r="D4" t="n">
-        <v>122.8028933334165</v>
+        <v>146.1969593779138</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.86020058203201</v>
+        <v>38.99992755120455</v>
       </c>
       <c r="C5" t="n">
-        <v>165.4735755507999</v>
+        <v>205.9215809657685</v>
       </c>
       <c r="D5" t="n">
-        <v>99.37741136238341</v>
+        <v>117.5397438909494</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.59883470852411</v>
+        <v>36.50825187782615</v>
       </c>
       <c r="C6" t="n">
-        <v>163.8644910635394</v>
+        <v>203.914888658288</v>
       </c>
       <c r="D6" t="n">
-        <v>52.28690098048088</v>
+        <v>58.64666260859173</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.20092378866788</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="C7" t="n">
-        <v>133.1878205489393</v>
+        <v>145.7640086403409</v>
       </c>
       <c r="D7" t="n">
-        <v>34.49468733641593</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.77039421039326</v>
+        <v>11.43245201595411</v>
       </c>
       <c r="C8" t="n">
-        <v>95.9658380901257</v>
+        <v>90.79202768874502</v>
       </c>
       <c r="D8" t="n">
-        <v>30.70906818884022</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>61.23749480009903</v>
+        <v>50.9203081761693</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>40.28601704376787</v>
+        <v>36.01541453029424</v>
       </c>
       <c r="D10" t="n">
         <v>30.7483380970101</v>
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.47308888692249</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>26.03594911662541</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.835287369864788</v>
+        <v>2.151990967709009</v>
       </c>
       <c r="C2" t="n">
-        <v>2.327723806769188</v>
+        <v>1.463785827031994</v>
       </c>
       <c r="D2" t="n">
-        <v>17.44271146135308</v>
+        <v>8.394924619014475</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.62928458288898</v>
+        <v>16.68971097219578</v>
       </c>
       <c r="C3" t="n">
-        <v>23.08579726536375</v>
+        <v>18.22614612934204</v>
       </c>
       <c r="D3" t="n">
-        <v>75.48167224101601</v>
+        <v>74.642277953885</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.66723825265188</v>
+        <v>40.2280939292173</v>
       </c>
       <c r="C4" t="n">
-        <v>91.75119519579417</v>
+        <v>96.26919813073798</v>
       </c>
       <c r="D4" t="n">
-        <v>130.8816951916635</v>
+        <v>154.3012866764712</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.62734644967627</v>
+        <v>40.32528695193774</v>
       </c>
       <c r="C5" t="n">
-        <v>192.5452684954057</v>
+        <v>234.6377013149877</v>
       </c>
       <c r="D5" t="n">
-        <v>107.5750046928443</v>
+        <v>123.6511233498858</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.91705983342032</v>
+        <v>29.94723197034471</v>
       </c>
       <c r="C6" t="n">
-        <v>199.5677098238831</v>
+        <v>240.020623977373</v>
       </c>
       <c r="D6" t="n">
-        <v>51.56237117474674</v>
+        <v>57.07684802950107</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.761517423326035</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="C7" t="n">
-        <v>135.2239652875472</v>
+        <v>141.1527396734936</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.87207936547421</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>76.10508203321274</v>
+        <v>65.08987279156352</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>30.7296848906294</v>
+        <v>27.40156017323271</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.7904711328347</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.848451000647497</v>
+        <v>2.539781310886498</v>
       </c>
       <c r="C2" t="n">
-        <v>3.033600406122644</v>
+        <v>6.526658737832795</v>
       </c>
       <c r="D2" t="n">
-        <v>12.96005144376214</v>
+        <v>15.94554621237669</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.33137306014569</v>
+        <v>12.20312396378785</v>
       </c>
       <c r="C3" t="n">
-        <v>15.60487975900305</v>
+        <v>11.849694790259</v>
       </c>
       <c r="D3" t="n">
-        <v>72.00137662946108</v>
+        <v>65.89981464756714</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.85569275413827</v>
+        <v>36.34822700203391</v>
       </c>
       <c r="C4" t="n">
-        <v>75.18518443433348</v>
+        <v>71.26702934668447</v>
       </c>
       <c r="D4" t="n">
-        <v>137.5693605529928</v>
+        <v>155.7179486136993</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.24909584610077</v>
+        <v>49.06284151973436</v>
       </c>
       <c r="C5" t="n">
-        <v>182.9486846863931</v>
+        <v>209.6522222419064</v>
       </c>
       <c r="D5" t="n">
-        <v>126.424560614383</v>
+        <v>144.8077863764046</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.03280825153021</v>
+        <v>39.72838434775569</v>
       </c>
       <c r="C6" t="n">
-        <v>249.8420280106581</v>
+        <v>301.2836442177825</v>
       </c>
       <c r="D6" t="n">
-        <v>69.35360307110744</v>
+        <v>75.91462297858888</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.61906619521901</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="C7" t="n">
-        <v>204.3331131802971</v>
+        <v>230.6233349523225</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>42.10028680121597</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.425538724295373</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>119.3314334511998</v>
+        <v>113.9907259400971</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>33.62976760897448</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>55.02499532762521</v>
+        <v>47.25937098703294</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.003166227290993</v>
+        <v>1.934042977366216</v>
       </c>
       <c r="C2" t="n">
-        <v>2.421971586376881</v>
+        <v>3.364449382453819</v>
       </c>
       <c r="D2" t="n">
-        <v>9.203884727313847</v>
+        <v>11.54829824505523</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.13854959948582</v>
+        <v>10.83358591636355</v>
       </c>
       <c r="C3" t="n">
-        <v>14.11753198706914</v>
+        <v>18.34395585385165</v>
       </c>
       <c r="D3" t="n">
-        <v>67.22026530977911</v>
+        <v>63.97068040872216</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.84445156103505</v>
+        <v>32.26415655236718</v>
       </c>
       <c r="C4" t="n">
-        <v>60.77607337910305</v>
+        <v>54.82864578677587</v>
       </c>
       <c r="D4" t="n">
-        <v>141.372651159245</v>
+        <v>154.5693037997306</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>69.45865007546185</v>
+        <v>52.52350217720437</v>
       </c>
       <c r="C5" t="n">
-        <v>171.8058482431918</v>
+        <v>186.8511318107742</v>
       </c>
       <c r="D5" t="n">
-        <v>140.9053392520235</v>
+        <v>160.9820798038708</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.09572222006002</v>
+        <v>47.17494068446774</v>
       </c>
       <c r="C6" t="n">
-        <v>276.2068626082062</v>
+        <v>327.0447039772188</v>
       </c>
       <c r="D6" t="n">
-        <v>81.79136473621028</v>
+        <v>91.17000055488006</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.36144738607885</v>
+        <v>14.97165248976386</v>
       </c>
       <c r="C7" t="n">
-        <v>260.8660729816455</v>
+        <v>299.6127096251543</v>
       </c>
       <c r="D7" t="n">
-        <v>44.79518424937346</v>
+        <v>47.07087542781757</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>158.9694970101648</v>
+        <v>158.2184600164159</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>34.71459882216722</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>66.11874438561416</v>
+        <v>56.24530772400399</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.391758391723482</v>
+        <v>2.700787934382975</v>
       </c>
       <c r="C2" t="n">
-        <v>10.004009106275</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="D2" t="n">
-        <v>12.2041057114921</v>
+        <v>10.56262354999143</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.68908907739002</v>
+        <v>8.767006998924016</v>
       </c>
       <c r="C3" t="n">
-        <v>11.90859965251381</v>
+        <v>15.9141302858408</v>
       </c>
       <c r="D3" t="n">
-        <v>60.74073046175016</v>
+        <v>59.12575548826416</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.13126075939537</v>
+        <v>26.77618688562751</v>
       </c>
       <c r="C4" t="n">
-        <v>48.52386203010285</v>
+        <v>50.66799901617789</v>
       </c>
       <c r="D4" t="n">
-        <v>140.517548908846</v>
+        <v>151.5573018431014</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.20692175254716</v>
+        <v>51.44357970253288</v>
       </c>
       <c r="C5" t="n">
-        <v>146.6731070144735</v>
+        <v>150.1337676719435</v>
       </c>
       <c r="D5" t="n">
-        <v>155.4597489674825</v>
+        <v>174.3829359668397</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>73.09700706740053</v>
+        <v>56.03030497677397</v>
       </c>
       <c r="C6" t="n">
-        <v>276.0056043288356</v>
+        <v>316.3780151705772</v>
       </c>
       <c r="D6" t="n">
-        <v>100.7901463087946</v>
+        <v>111.5373384271844</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.84833749412304</v>
+        <v>28.50602634051038</v>
       </c>
       <c r="C7" t="n">
-        <v>318.1176721025025</v>
+        <v>369.0811771776586</v>
       </c>
       <c r="D7" t="n">
-        <v>54.07760879302705</v>
+        <v>56.53295980134833</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>234.5738877142116</v>
+        <v>251.0967015766854</v>
       </c>
       <c r="D8" t="n">
-        <v>38.80357801035517</v>
+        <v>38.30288668118931</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.995312245657018</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>114.3765527878661</v>
+        <v>106.4999909566939</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>49.68134257340984</v>
+        <v>42.99073196896783</v>
       </c>
       <c r="D10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
         <v>16.91060420565131</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.578290455530377</v>
+        <v>3.882812170296135</v>
       </c>
       <c r="C2" t="n">
-        <v>4.723188205131405</v>
+        <v>2.298271375641783</v>
       </c>
       <c r="D2" t="n">
-        <v>6.117269945161876</v>
+        <v>13.35078703005238</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.814089830998858</v>
+        <v>1.932079481957723</v>
       </c>
       <c r="C2" t="n">
-        <v>5.6018524004323</v>
+        <v>3.127848185730338</v>
       </c>
       <c r="D2" t="n">
-        <v>8.982009746154068</v>
+        <v>7.773478322226245</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.77945092390974</v>
+        <v>11.90369091399258</v>
       </c>
       <c r="C3" t="n">
-        <v>22.06477965294707</v>
+        <v>19.98347451994383</v>
       </c>
       <c r="D3" t="n">
-        <v>65.84581852383357</v>
+        <v>64.05412896358314</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.8466770983508</v>
+        <v>38.33921134624644</v>
       </c>
       <c r="C4" t="n">
-        <v>72.8368439257751</v>
+        <v>76.98472797621788</v>
       </c>
       <c r="D4" t="n">
-        <v>144.0783478321491</v>
+        <v>157.0707969501514</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.68777283898307</v>
+        <v>32.98672286269284</v>
       </c>
       <c r="C5" t="n">
-        <v>227.4463993813798</v>
+        <v>249.241198415659</v>
       </c>
       <c r="D5" t="n">
-        <v>143.5315143608837</v>
+        <v>158.8713222397401</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.46671537461151</v>
+        <v>17.67047692873834</v>
       </c>
       <c r="C6" t="n">
-        <v>266.3049552631728</v>
+        <v>305.1075515258238</v>
       </c>
       <c r="D6" t="n">
-        <v>80.34230512474198</v>
+        <v>87.02407999984578</v>
       </c>
     </row>
     <row r="7">
@@ -4271,10 +4271,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.94684675525043</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>164.9277238272387</v>
+        <v>176.5457261592954</v>
       </c>
       <c r="D7" t="n">
         <v>34.13536767666159</v>
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>84.28304040958866</v>
+        <v>78.44164156932014</v>
       </c>
       <c r="D8" t="n">
-        <v>25.36836067773758</v>
+        <v>24.61732368398877</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>37.94062177832222</v>
+        <v>32.72655972106742</v>
       </c>
       <c r="D9" t="n">
-        <v>20.74531073843935</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.63419332141022</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.3600647277471</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>16.17036643664921</v>
       </c>
       <c r="D11" t="n">
-        <v>16.8811517745239</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
         <v>13.66887328622834</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.154576357923254</v>
+        <v>5.269039928692631</v>
       </c>
       <c r="C2" t="n">
-        <v>3.238785676310227</v>
+        <v>4.186172210908399</v>
       </c>
       <c r="D2" t="n">
-        <v>15.17585601224719</v>
+        <v>23.26447534753666</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.849694790259</v>
+        <v>8.256498192715675</v>
       </c>
       <c r="C3" t="n">
-        <v>12.09022297779947</v>
+        <v>5.787402716534947</v>
       </c>
       <c r="D3" t="n">
-        <v>8.51666133434108</v>
+        <v>14.34824269756713</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39918489694889</v>
+        <v>13.39864927875083</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14867387226182</v>
+        <v>70.14586975346022</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576374693758692</v>
+        <v>1.576311679853038</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.543528375254239</v>
+        <v>4.068362486398782</v>
       </c>
       <c r="C2" t="n">
-        <v>3.240749171718721</v>
+        <v>4.201880174176349</v>
       </c>
       <c r="D2" t="n">
-        <v>13.003248342749</v>
+        <v>19.79301546531994</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.49965282819939</v>
+        <v>14.19116306488765</v>
       </c>
       <c r="C3" t="n">
-        <v>12.43874341280709</v>
+        <v>12.49273953654066</v>
       </c>
       <c r="D3" t="n">
-        <v>19.20298509506761</v>
+        <v>30.41945261608742</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.80926320793563</v>
+        <v>9.750718198579321</v>
       </c>
       <c r="C4" t="n">
-        <v>19.25894471420968</v>
+        <v>9.508226515630358</v>
       </c>
       <c r="D4" t="n">
-        <v>19.52696183746906</v>
+        <v>22.59001467471911</v>
       </c>
     </row>
     <row r="5">
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
         <v>16.54343056426301</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4994,7 +4994,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44470620670441</v>
+        <v>15.44332022721125</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16520304792986</v>
+        <v>86.1574707412838</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251517096148297</v>
+        <v>3.251225310991841</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.891467973185108</v>
+        <v>4.968625131193107</v>
       </c>
       <c r="C2" t="n">
-        <v>7.215845626214056</v>
+        <v>8.202502068982101</v>
       </c>
       <c r="D2" t="n">
-        <v>25.8994861857351</v>
+        <v>32.03835458039041</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.53754007803752</v>
+        <v>14.29915531235479</v>
       </c>
       <c r="C3" t="n">
-        <v>12.55164439879547</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D3" t="n">
-        <v>25.14746744428205</v>
+        <v>39.1962770920539</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.49991487010665</v>
+        <v>19.71840263979719</v>
       </c>
       <c r="C4" t="n">
-        <v>26.39330528097125</v>
+        <v>22.21989579021806</v>
       </c>
       <c r="D4" t="n">
-        <v>24.58099901893164</v>
+        <v>32.53217367562655</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.34547738090364</v>
+        <v>9.179341034707679</v>
       </c>
       <c r="C5" t="n">
-        <v>22.89926520155685</v>
+        <v>12.44365215132832</v>
       </c>
       <c r="D5" t="n">
-        <v>29.82058651649687</v>
+        <v>30.97414006898687</v>
       </c>
     </row>
     <row r="6">
@@ -5218,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
         <v>29.6242369756475</v>
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>40.82499653339935</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.82369599052563</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5277,7 +5277,7 @@
         <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>45.77987719673301</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.7448264121103</v>
+        <v>16.74246559163759</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1434411138728</v>
+        <v>102.1290401089893</v>
       </c>
       <c r="D21" t="n">
-        <v>5.02344792363309</v>
+        <v>5.022739677491275</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.132977908429824</v>
+        <v>4.711407232680442</v>
       </c>
       <c r="C2" t="n">
-        <v>4.035964812158637</v>
+        <v>7.712609964562943</v>
       </c>
       <c r="D2" t="n">
-        <v>27.06874770149305</v>
+        <v>26.30887497840602</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.54030539470102</v>
+        <v>15.79632056133118</v>
       </c>
       <c r="C3" t="n">
-        <v>21.63281066307847</v>
+        <v>24.81858196335937</v>
       </c>
       <c r="D3" t="n">
-        <v>39.23554700022378</v>
+        <v>54.82570054366313</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.94584931201296</v>
+        <v>23.95562573132642</v>
       </c>
       <c r="C4" t="n">
-        <v>29.25215459573796</v>
+        <v>30.69434197327653</v>
       </c>
       <c r="D4" t="n">
-        <v>31.03893541746715</v>
+        <v>43.87823189360694</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.59907138823559</v>
+        <v>19.61041039233004</v>
       </c>
       <c r="C5" t="n">
-        <v>37.11006322052944</v>
+        <v>28.17615911188346</v>
       </c>
       <c r="D5" t="n">
-        <v>32.07860623626453</v>
+        <v>35.78470381979624</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.3107153006275</v>
+        <v>9.217629195173304</v>
       </c>
       <c r="C6" t="n">
-        <v>24.83527167433157</v>
+        <v>16.1006623496477</v>
       </c>
       <c r="D6" t="n">
-        <v>37.8768081775462</v>
+        <v>38.56108632740622</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5549,7 +5549,7 @@
         <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.60155896745857</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
         <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5588,7 +5588,7 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
         <v>47.29864089520282</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07944581291</v>
+        <v>18.07572156093772</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9468607794605</v>
+        <v>117.9225644689747</v>
       </c>
       <c r="D21" t="n">
-        <v>6.887407928727619</v>
+        <v>6.885989166071512</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.381360077604268</v>
+        <v>6.418666490365646</v>
       </c>
       <c r="C2" t="n">
-        <v>12.33173291304418</v>
+        <v>14.80181013692916</v>
       </c>
       <c r="D2" t="n">
-        <v>24.95799013736241</v>
+        <v>27.42512211813465</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.85308200172825</v>
+        <v>14.30406405087603</v>
       </c>
       <c r="C3" t="n">
-        <v>17.08731879241574</v>
+        <v>26.1783025337412</v>
       </c>
       <c r="D3" t="n">
-        <v>48.05164138436013</v>
+        <v>58.91958847037233</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.930100291016</v>
+        <v>20.16509784522949</v>
       </c>
       <c r="C4" t="n">
-        <v>36.41204060280995</v>
+        <v>40.73860273542564</v>
       </c>
       <c r="D4" t="n">
-        <v>37.30543101367455</v>
+        <v>52.48030527821749</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.52481841561132</v>
+        <v>17.30330328735004</v>
       </c>
       <c r="C5" t="n">
-        <v>34.23845118560752</v>
+        <v>32.34858685493241</v>
       </c>
       <c r="D5" t="n">
-        <v>29.28062527916113</v>
+        <v>35.31837366027901</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.67927160034756</v>
+        <v>9.861655689159212</v>
       </c>
       <c r="C6" t="n">
-        <v>29.22270216461057</v>
+        <v>21.25287430153496</v>
       </c>
       <c r="D6" t="n">
-        <v>30.43025184083414</v>
+        <v>31.63780151705772</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>18.44507586738907</v>
+        <v>14.31289978021425</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
         <v>32.32797015314322</v>
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.070336564821941</v>
+        <v>7.068517113011851</v>
       </c>
       <c r="C21" t="n">
-        <v>67.16819736580844</v>
+        <v>67.15091257361259</v>
       </c>
       <c r="D21" t="n">
-        <v>5.302752423616456</v>
+        <v>5.301387834758889</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.254313713128929</v>
+        <v>4.683918296961532</v>
       </c>
       <c r="C2" t="n">
-        <v>6.695519342963247</v>
+        <v>9.69868557025424</v>
       </c>
       <c r="D2" t="n">
-        <v>18.40875120233194</v>
+        <v>24.38857646889926</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.77869016038374</v>
+        <v>19.5907754382451</v>
       </c>
       <c r="C3" t="n">
-        <v>37.80219535202343</v>
+        <v>46.93735774004001</v>
       </c>
       <c r="D3" t="n">
-        <v>57.94274950464675</v>
+        <v>68.25110039923827</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.14103717870883</v>
+        <v>25.04045694451915</v>
       </c>
       <c r="C4" t="n">
-        <v>40.64926369433918</v>
+        <v>56.6792402092811</v>
       </c>
       <c r="D4" t="n">
-        <v>54.67549314491337</v>
+        <v>72.14765703739384</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.11511082777092</v>
+        <v>25.15728492132452</v>
       </c>
       <c r="C5" t="n">
-        <v>55.14967728606459</v>
+        <v>59.02758071783948</v>
       </c>
       <c r="D5" t="n">
-        <v>36.66827675361837</v>
+        <v>47.46750150033328</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.58117894538089</v>
+        <v>17.75098024048658</v>
       </c>
       <c r="C6" t="n">
-        <v>44.59883470852411</v>
+        <v>39.28561613314037</v>
       </c>
       <c r="D6" t="n">
-        <v>33.52962934314132</v>
+        <v>35.90447703971436</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.25868267230242</v>
+        <v>9.102764713776425</v>
       </c>
       <c r="C7" t="n">
-        <v>32.87774886752143</v>
+        <v>23.95464398362217</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>33.95570784678443</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>22.5311098124643</v>
+        <v>19.3600647277471</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
         <v>23.51874800293658</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.28437234352885</v>
       </c>
     </row>
     <row r="10">
@@ -6185,7 +6185,7 @@
         <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.298550174680632</v>
+        <v>7.294577623113382</v>
       </c>
       <c r="C21" t="n">
-        <v>77.54709560598172</v>
+        <v>77.50488724557968</v>
       </c>
       <c r="D21" t="n">
-        <v>6.386231402845554</v>
+        <v>6.382755420224209</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.005350706877739</v>
+        <v>4.776202581160732</v>
       </c>
       <c r="C2" t="n">
-        <v>5.775621744083985</v>
+        <v>7.642905877561418</v>
       </c>
       <c r="D2" t="n">
-        <v>21.19495118698439</v>
+        <v>22.47122320250524</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.56623174563893</v>
+        <v>17.71072858461246</v>
       </c>
       <c r="C3" t="n">
-        <v>30.48817495538469</v>
+        <v>41.29721717914208</v>
       </c>
       <c r="D3" t="n">
-        <v>59.40555358397449</v>
+        <v>71.92283681312134</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.53966780436203</v>
+        <v>32.78742807873073</v>
       </c>
       <c r="C4" t="n">
-        <v>73.55155625446679</v>
+        <v>93.14233169271189</v>
       </c>
       <c r="D4" t="n">
-        <v>72.3518605598772</v>
+        <v>89.47943100816704</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.73623832938966</v>
+        <v>32.00497515844602</v>
       </c>
       <c r="C5" t="n">
-        <v>67.02882450745099</v>
+        <v>85.60839981032187</v>
       </c>
       <c r="D5" t="n">
-        <v>48.69468613064181</v>
+        <v>63.54362015737481</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.68434456978482</v>
+        <v>26.92835777978577</v>
       </c>
       <c r="C6" t="n">
-        <v>69.15234479173684</v>
+        <v>69.71586797397451</v>
       </c>
       <c r="D6" t="n">
-        <v>37.55479493055324</v>
+        <v>43.02902012943346</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.06201433628357</v>
+        <v>15.69029180927252</v>
       </c>
       <c r="C7" t="n">
-        <v>50.90361846519711</v>
+        <v>41.9206269713388</v>
       </c>
       <c r="D7" t="n">
-        <v>36.4110588551057</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>34.38080460272329</v>
+        <v>26.62008900065226</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>26.73593522975338</v>
+        <v>24.51718541815559</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6552,7 +6552,7 @@
         <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6636,7 +6636,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.515570335661844</v>
+        <v>7.507788138967568</v>
       </c>
       <c r="C21" t="n">
-        <v>87.36850515206893</v>
+        <v>87.27803711549797</v>
       </c>
       <c r="D21" t="n">
-        <v>7.515570335661844</v>
+        <v>7.507788138967568</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_49_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_49_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497655442673</v>
+        <v>10.84497652184451</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907271620098</v>
+        <v>37.78907260266897</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.89401230567035</v>
+        <v>1.043597809614359</v>
       </c>
       <c r="C2" t="n">
-        <v>9.410051745205678</v>
+        <v>2.236421270274234</v>
       </c>
       <c r="D2" t="n">
-        <v>30.67372527148734</v>
+        <v>13.44896180047705</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.93514789825748</v>
+        <v>8.521570072862314</v>
       </c>
       <c r="C3" t="n">
-        <v>34.65078522139117</v>
+        <v>30.99868376159304</v>
       </c>
       <c r="D3" t="n">
-        <v>73.00275928779283</v>
+        <v>74.06304680837938</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.68081848959532</v>
+        <v>16.57877348161589</v>
       </c>
       <c r="C4" t="n">
-        <v>98.70687768038282</v>
+        <v>104.8840342355037</v>
       </c>
       <c r="D4" t="n">
-        <v>104.5394407913131</v>
+        <v>85.59956408098364</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.47254910757476</v>
+        <v>17.03332266868216</v>
       </c>
       <c r="C5" t="n">
-        <v>130.5724446648258</v>
+        <v>99.1319744363217</v>
       </c>
       <c r="D5" t="n">
-        <v>79.74245727744719</v>
+        <v>51.88536616944394</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.26045054572845</v>
+        <v>11.14970867713103</v>
       </c>
       <c r="C6" t="n">
-        <v>104.2115370580947</v>
+        <v>43.87430490278997</v>
       </c>
       <c r="D6" t="n">
-        <v>52.97117913034091</v>
+        <v>31.23528495831652</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.19419042345839</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>72.16336500066178</v>
+        <v>27.30829414132927</v>
       </c>
       <c r="D7" t="n">
-        <v>40.78278138211675</v>
+        <v>29.46421209985527</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.51728322914683</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>41.22358610132356</v>
+        <v>27.53802310412303</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>32.17187226816797</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>28.75539025738908</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.706067559629497</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>96.32584449536873</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.669326004583185</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.188937527571892</v>
+        <v>1.883973844449629</v>
       </c>
       <c r="C2" t="n">
-        <v>7.394523708386976</v>
+        <v>4.120395114723864</v>
       </c>
       <c r="D2" t="n">
-        <v>25.64128653951819</v>
+        <v>14.34726094986289</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.58662746324986</v>
+        <v>5.85121631731099</v>
       </c>
       <c r="C3" t="n">
-        <v>35.45090960035233</v>
+        <v>17.7745421853885</v>
       </c>
       <c r="D3" t="n">
-        <v>79.02578145334701</v>
+        <v>67.637508084084</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.96610616090365</v>
+        <v>16.77021428394402</v>
       </c>
       <c r="C4" t="n">
-        <v>91.55975439346602</v>
+        <v>89.17312572444203</v>
       </c>
       <c r="D4" t="n">
-        <v>114.264633549582</v>
+        <v>103.5311858990516</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.86587008407924</v>
+        <v>21.23029410433728</v>
       </c>
       <c r="C5" t="n">
-        <v>155.7051858935442</v>
+        <v>153.1526418625024</v>
       </c>
       <c r="D5" t="n">
-        <v>97.09484795000957</v>
+        <v>71.34851440613696</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.11581483803468</v>
+        <v>17.06670209062656</v>
       </c>
       <c r="C6" t="n">
-        <v>151.7487426454295</v>
+        <v>104.2115370580947</v>
       </c>
       <c r="D6" t="n">
-        <v>64.20139111922018</v>
+        <v>39.56737772425921</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.69808903764427</v>
+        <v>9.402197763571703</v>
       </c>
       <c r="C7" t="n">
-        <v>109.4727230051533</v>
+        <v>46.11268966847268</v>
       </c>
       <c r="D7" t="n">
-        <v>45.51382356888213</v>
+        <v>31.79978988825843</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.69247628885927</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>66.34160111447821</v>
+        <v>32.87873061522568</v>
       </c>
       <c r="D8" t="n">
-        <v>38.88702656521616</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.540624189870499</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>40.04843409934012</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>36.16562192904399</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>35.3036474447153</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.887631109935298</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104.5111122066427</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.859538887419122</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.42062998577414</v>
+        <v>0.9856746950637977</v>
       </c>
       <c r="C2" t="n">
-        <v>6.287112297996573</v>
+        <v>1.66504410640259</v>
       </c>
       <c r="D2" t="n">
-        <v>23.77007541522377</v>
+        <v>9.686904597803277</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.16724126708723</v>
+        <v>6.621888265144737</v>
       </c>
       <c r="C3" t="n">
-        <v>31.98043146583985</v>
+        <v>18.13288009743859</v>
       </c>
       <c r="D3" t="n">
-        <v>80.1351563591459</v>
+        <v>66.32196616039327</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.65154598491717</v>
+        <v>18.30174070256904</v>
       </c>
       <c r="C4" t="n">
-        <v>89.91336349344414</v>
+        <v>79.4096448057075</v>
       </c>
       <c r="D4" t="n">
-        <v>124.7938776776291</v>
+        <v>113.6775484224424</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.51029748869265</v>
+        <v>21.67208057124834</v>
       </c>
       <c r="C5" t="n">
-        <v>159.5585456327129</v>
+        <v>175.6346642897544</v>
       </c>
       <c r="D5" t="n">
-        <v>110.8638595020711</v>
+        <v>82.07410807503337</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.36111289537615</v>
+        <v>13.64531134132642</v>
       </c>
       <c r="C6" t="n">
-        <v>191.6381336166817</v>
+        <v>141.3638154299067</v>
       </c>
       <c r="D6" t="n">
-        <v>77.0014176871901</v>
+        <v>40.09064925062275</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.8426679920758</v>
+        <v>4.431609136970102</v>
       </c>
       <c r="C7" t="n">
-        <v>157.2622377524796</v>
+        <v>47.9691745772034</v>
       </c>
       <c r="D7" t="n">
-        <v>51.44259795482861</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.61870634232051</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>99.38722883942584</v>
+        <v>37.1346069131356</v>
       </c>
       <c r="D8" t="n">
-        <v>41.80772598535042</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.42343636016663</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>58.3531200450219</v>
+        <v>26.95781021091316</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>38.72012945549421</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>36.58482819875739</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>34.47308888692249</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.052986985456828</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112.7418177963956</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.07285710500314</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.917975161199774</v>
+        <v>0.6086835766330224</v>
       </c>
       <c r="C2" t="n">
-        <v>4.274529504290612</v>
+        <v>4.357978059151591</v>
       </c>
       <c r="D2" t="n">
-        <v>19.63102709411922</v>
+        <v>15.34275312196915</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.97642235956485</v>
+        <v>4.952917167925158</v>
       </c>
       <c r="C3" t="n">
-        <v>48.41488803493146</v>
+        <v>11.45208697003904</v>
       </c>
       <c r="D3" t="n">
-        <v>88.59291283123217</v>
+        <v>58.9294059474148</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.33476027161494</v>
+        <v>15.80024755214817</v>
       </c>
       <c r="C4" t="n">
-        <v>129.7075249373843</v>
+        <v>61.1717177039145</v>
       </c>
       <c r="D4" t="n">
-        <v>121.3096550752571</v>
+        <v>120.9267734706009</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.93701358267474</v>
+        <v>24.88730430265665</v>
       </c>
       <c r="C5" t="n">
-        <v>114.4963260077843</v>
+        <v>161.9883712007237</v>
       </c>
       <c r="D5" t="n">
-        <v>75.79092276785377</v>
+        <v>103.9425381871311</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.35854320069512</v>
+        <v>20.68935111929729</v>
       </c>
       <c r="C6" t="n">
-        <v>103.5675105641088</v>
+        <v>213.0520145417131</v>
       </c>
       <c r="D6" t="n">
-        <v>33.85164259013428</v>
+        <v>54.05797383894213</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.94791061841269</v>
+        <v>8.982991493858314</v>
       </c>
       <c r="C7" t="n">
-        <v>69.88767382221769</v>
+        <v>122.048911096555</v>
       </c>
       <c r="D7" t="n">
-        <v>29.34443887993716</v>
+        <v>37.30935800449154</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>42.97600575340412</v>
+        <v>50.06913291658733</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>36.0546844384641</v>
       </c>
       <c r="D9" t="n">
-        <v>27.84531013555227</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.630503010304705</v>
+        <v>0.460439673291754</v>
       </c>
       <c r="C2" t="n">
-        <v>2.535854320069511</v>
+        <v>2.991385254840031</v>
       </c>
       <c r="D2" t="n">
-        <v>14.89998490735384</v>
+        <v>11.16247139728623</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.87333885061894</v>
+        <v>3.696280106489241</v>
       </c>
       <c r="C3" t="n">
-        <v>32.59402378099411</v>
+        <v>14.5593184539802</v>
       </c>
       <c r="D3" t="n">
-        <v>84.78864047727578</v>
+        <v>57.95256698168922</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.30695254072654</v>
+        <v>13.63058512576272</v>
       </c>
       <c r="C4" t="n">
-        <v>130.1797455831271</v>
+        <v>46.58392856651115</v>
       </c>
       <c r="D4" t="n">
-        <v>136.6887328622834</v>
+        <v>123.3644530202457</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.12769362147687</v>
+        <v>26.08994524035899</v>
       </c>
       <c r="C5" t="n">
-        <v>173.3030134921682</v>
+        <v>145.6668156176205</v>
       </c>
       <c r="D5" t="n">
-        <v>94.59139130418019</v>
+        <v>120.0432005367788</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.71201343195298</v>
+        <v>24.91577498607981</v>
       </c>
       <c r="C6" t="n">
-        <v>137.9424246806066</v>
+        <v>243.5225180384214</v>
       </c>
       <c r="D6" t="n">
-        <v>43.1095234411817</v>
+        <v>66.73724543928969</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.92983824910874</v>
+        <v>10.42027013287564</v>
       </c>
       <c r="C7" t="n">
-        <v>99.11233948223673</v>
+        <v>189.5411205204104</v>
       </c>
       <c r="D7" t="n">
-        <v>32.15910954801276</v>
+        <v>41.98051358129786</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>58.16364273810228</v>
+        <v>80.77820110542756</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>40.47254910757476</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>34.83437204208531</v>
+        <v>45.70624611891449</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.618722037853743</v>
+        <v>1.488329519638165</v>
       </c>
       <c r="C2" t="n">
-        <v>3.079742548222244</v>
+        <v>5.896376711706344</v>
       </c>
       <c r="D2" t="n">
-        <v>12.02935462013617</v>
+        <v>14.33842522052467</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.0529576227671</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C3" t="n">
-        <v>20.60197557361932</v>
+        <v>12.92961726493049</v>
       </c>
       <c r="D3" t="n">
-        <v>78.28456193664067</v>
+        <v>54.21210822850887</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.61624412529329</v>
+        <v>10.51648140789183</v>
       </c>
       <c r="C4" t="n">
-        <v>105.2158649595392</v>
+        <v>41.69580674706629</v>
       </c>
       <c r="D4" t="n">
-        <v>146.1969593779138</v>
+        <v>122.8794696543478</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.99992755120455</v>
+        <v>23.88101290580367</v>
       </c>
       <c r="C5" t="n">
-        <v>205.9215809657685</v>
+        <v>116.2389281828224</v>
       </c>
       <c r="D5" t="n">
-        <v>117.5397438909494</v>
+        <v>135.505726878666</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.50825187782615</v>
+        <v>29.78622534684823</v>
       </c>
       <c r="C6" t="n">
-        <v>203.914888658288</v>
+        <v>241.4294319329671</v>
       </c>
       <c r="D6" t="n">
-        <v>58.64666260859173</v>
+        <v>85.8165303236222</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.37385025333556</v>
+        <v>18.38518925743002</v>
       </c>
       <c r="C7" t="n">
-        <v>145.7640086403409</v>
+        <v>263.9202900895573</v>
       </c>
       <c r="D7" t="n">
-        <v>36.17151241526948</v>
+        <v>49.94543270585223</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.43245201595411</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C8" t="n">
-        <v>90.79202768874502</v>
+        <v>156.9667316935013</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>42.89255719854314</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>50.9203081761693</v>
+        <v>69.66874408417063</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>42.48905889209769</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>36.01541453029424</v>
+        <v>42.70602513473626</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.58460721457913</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>42.98484148274235</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.151990967709009</v>
+        <v>0.9876381904722912</v>
       </c>
       <c r="C2" t="n">
-        <v>1.463785827031994</v>
+        <v>3.019855938263189</v>
       </c>
       <c r="D2" t="n">
-        <v>8.394924619014475</v>
+        <v>10.32307711015521</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.68971097219578</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C3" t="n">
-        <v>18.22614612934204</v>
+        <v>18.6679325962531</v>
       </c>
       <c r="D3" t="n">
-        <v>74.642277953885</v>
+        <v>59.52336330848411</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.2280939292173</v>
+        <v>16.64258708239193</v>
       </c>
       <c r="C4" t="n">
-        <v>96.26919813073798</v>
+        <v>60.91646330081034</v>
       </c>
       <c r="D4" t="n">
-        <v>154.3012866764712</v>
+        <v>128.2908630001562</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.32528695193774</v>
+        <v>18.53048791765855</v>
       </c>
       <c r="C5" t="n">
-        <v>234.6377013149877</v>
+        <v>189.3300447639974</v>
       </c>
       <c r="D5" t="n">
-        <v>123.6511233498858</v>
+        <v>126.0809489178966</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.94723197034471</v>
+        <v>11.39121861237574</v>
       </c>
       <c r="C6" t="n">
-        <v>240.020623977373</v>
+        <v>235.3514318959751</v>
       </c>
       <c r="D6" t="n">
-        <v>57.07684802950107</v>
+        <v>71.68819911180636</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.545712854840985</v>
+        <v>4.611268966847268</v>
       </c>
       <c r="C7" t="n">
-        <v>141.1527396734936</v>
+        <v>110.3710221545391</v>
       </c>
       <c r="D7" t="n">
-        <v>35.87207936547421</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>65.08987279156352</v>
+        <v>51.32086123950201</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>27.40156017323271</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>26.84687272033327</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>21.67895280517806</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>36.19212911705866</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.539781310886498</v>
+        <v>0.5026548245743669</v>
       </c>
       <c r="C2" t="n">
-        <v>6.526658737832795</v>
+        <v>1.508946221427348</v>
       </c>
       <c r="D2" t="n">
-        <v>15.94554621237669</v>
+        <v>7.081346190732242</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.20312396378785</v>
+        <v>3.853359739168731</v>
       </c>
       <c r="C3" t="n">
-        <v>11.849694790259</v>
+        <v>14.84402528821177</v>
       </c>
       <c r="D3" t="n">
-        <v>65.89981464756714</v>
+        <v>54.11393345808418</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.34822700203391</v>
+        <v>11.69065166217102</v>
       </c>
       <c r="C4" t="n">
-        <v>71.26702934668447</v>
+        <v>51.71454206890498</v>
       </c>
       <c r="D4" t="n">
-        <v>155.7179486136993</v>
+        <v>123.6579955838155</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.06284151973436</v>
+        <v>17.42602175038089</v>
       </c>
       <c r="C5" t="n">
-        <v>209.6522222419064</v>
+        <v>136.0211444233956</v>
       </c>
       <c r="D5" t="n">
-        <v>144.8077863764046</v>
+        <v>127.9953569411779</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.72838434775569</v>
+        <v>11.23021198887927</v>
       </c>
       <c r="C6" t="n">
-        <v>301.2836442177825</v>
+        <v>223.1954318219911</v>
       </c>
       <c r="D6" t="n">
-        <v>75.91462297858888</v>
+        <v>77.40393424593128</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.58859095865835</v>
+        <v>4.07228947721577</v>
       </c>
       <c r="C7" t="n">
-        <v>230.6233349523225</v>
+        <v>154.0882474246496</v>
       </c>
       <c r="D7" t="n">
-        <v>42.10028680121597</v>
+        <v>37.36924461445059</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>113.9907259400971</v>
+        <v>60.16640805476577</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>47.25937098703294</v>
+        <v>29.28749751309084</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>21.52187317249857</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>18.93300447639974</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>13.86031408855647</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.934042977366216</v>
+        <v>0.5095270585040946</v>
       </c>
       <c r="C2" t="n">
-        <v>3.364449382453819</v>
+        <v>5.483060928218435</v>
       </c>
       <c r="D2" t="n">
-        <v>11.54829824505523</v>
+        <v>11.23806597051324</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.83358591636355</v>
+        <v>2.675262494072558</v>
       </c>
       <c r="C3" t="n">
-        <v>18.34395585385165</v>
+        <v>9.316785713302229</v>
       </c>
       <c r="D3" t="n">
-        <v>63.97068040872216</v>
+        <v>47.22206457427158</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.26415655236718</v>
+        <v>9.559277396251193</v>
       </c>
       <c r="C4" t="n">
-        <v>54.82864578677587</v>
+        <v>43.57192660988194</v>
       </c>
       <c r="D4" t="n">
-        <v>154.5693037997306</v>
+        <v>123.1602494977624</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.52350217720437</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="C5" t="n">
-        <v>186.8511318107742</v>
+        <v>113.1709666070511</v>
       </c>
       <c r="D5" t="n">
-        <v>160.9820798038708</v>
+        <v>144.1205629834318</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.17494068446774</v>
+        <v>17.54972196111598</v>
       </c>
       <c r="C6" t="n">
-        <v>327.0447039772188</v>
+        <v>222.7526636073758</v>
       </c>
       <c r="D6" t="n">
-        <v>91.17000055488006</v>
+        <v>99.22033172970391</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.97165248976386</v>
+        <v>8.503898614185871</v>
       </c>
       <c r="C7" t="n">
-        <v>299.6127096251543</v>
+        <v>246.1938535416769</v>
       </c>
       <c r="D7" t="n">
-        <v>47.07087542781757</v>
+        <v>49.94543270585223</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>2.670353755551324</v>
       </c>
       <c r="C8" t="n">
-        <v>158.2184600164159</v>
+        <v>134.9363132102029</v>
       </c>
       <c r="D8" t="n">
-        <v>34.71459882216722</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>56.24530772400399</v>
+        <v>52.36249555370786</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>23.40781051235669</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>21.06830573313655</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>17.94732978133594</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>13.88583952886689</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.700787934382975</v>
+        <v>0.4682936549257286</v>
       </c>
       <c r="C2" t="n">
-        <v>5.507604620824606</v>
+        <v>4.847870163570749</v>
       </c>
       <c r="D2" t="n">
-        <v>10.56262354999143</v>
+        <v>22.01863751084746</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.767006998924016</v>
+        <v>2.164753687864217</v>
       </c>
       <c r="C3" t="n">
-        <v>15.9141302858408</v>
+        <v>16.08593613408399</v>
       </c>
       <c r="D3" t="n">
-        <v>59.12575548826416</v>
+        <v>45.25856916577796</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.77618688562751</v>
+        <v>7.274750488468865</v>
       </c>
       <c r="C4" t="n">
-        <v>50.66799901617789</v>
+        <v>32.4428346345401</v>
       </c>
       <c r="D4" t="n">
-        <v>151.5573018431014</v>
+        <v>119.344196171355</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.44357970253288</v>
+        <v>16.51790512395259</v>
       </c>
       <c r="C5" t="n">
-        <v>150.1337676719435</v>
+        <v>95.86766331970105</v>
       </c>
       <c r="D5" t="n">
-        <v>174.3829359668397</v>
+        <v>155.7542732787565</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.03030497677397</v>
+        <v>21.1321193339126</v>
       </c>
       <c r="C6" t="n">
-        <v>316.3780151705772</v>
+        <v>202.1840674557009</v>
       </c>
       <c r="D6" t="n">
-        <v>111.5373384271844</v>
+        <v>119.2656563550153</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.50602634051038</v>
+        <v>14.49255961009142</v>
       </c>
       <c r="C7" t="n">
-        <v>369.0811771776586</v>
+        <v>286.9766349237937</v>
       </c>
       <c r="D7" t="n">
-        <v>56.53295980134833</v>
+        <v>65.6956111250838</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.844164156932015</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>251.0967015766854</v>
+        <v>230.7352541906066</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>36.55046702910875</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>106.4999909566939</v>
+        <v>108.2749908059722</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>25.73749781453438</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>42.99073196896783</v>
+        <v>43.84485247166256</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>21.78007281871549</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>19.19120412261664</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.882812170296135</v>
+        <v>2.925608158655495</v>
       </c>
       <c r="C2" t="n">
-        <v>2.298271375641783</v>
+        <v>3.603014074585794</v>
       </c>
       <c r="D2" t="n">
-        <v>13.35078703005238</v>
+        <v>9.92939628075224</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.932079481957723</v>
+        <v>0.585121631731099</v>
       </c>
       <c r="C2" t="n">
-        <v>3.127848185730338</v>
+        <v>10.06389571623405</v>
       </c>
       <c r="D2" t="n">
-        <v>7.773478322226245</v>
+        <v>24.26291276275567</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.90369091399258</v>
+        <v>1.855503161026472</v>
       </c>
       <c r="C3" t="n">
-        <v>19.98347451994383</v>
+        <v>17.41620427333842</v>
       </c>
       <c r="D3" t="n">
-        <v>64.05412896358314</v>
+        <v>51.03124566674921</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.33921134624644</v>
+        <v>5.730461349688633</v>
       </c>
       <c r="C4" t="n">
-        <v>76.98472797621788</v>
+        <v>36.25888796094745</v>
       </c>
       <c r="D4" t="n">
-        <v>157.0707969501514</v>
+        <v>115.4388038038612</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.98672286269284</v>
+        <v>14.06353586333556</v>
       </c>
       <c r="C5" t="n">
-        <v>249.241198415659</v>
+        <v>77.50898125028569</v>
       </c>
       <c r="D5" t="n">
-        <v>158.8713222397401</v>
+        <v>160.8348176482337</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.67047692873834</v>
+        <v>22.05790741901734</v>
       </c>
       <c r="C6" t="n">
-        <v>305.1075515258238</v>
+        <v>179.8846501014388</v>
       </c>
       <c r="D6" t="n">
-        <v>87.02407999984578</v>
+        <v>138.5461995187184</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>19.28348840681585</v>
       </c>
       <c r="C7" t="n">
-        <v>176.5457261592954</v>
+        <v>292.9054093097401</v>
       </c>
       <c r="D7" t="n">
-        <v>34.13536767666159</v>
+        <v>80.78703683476577</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="C8" t="n">
-        <v>78.44164156932014</v>
+        <v>299.5803119509142</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>44.2277340763188</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>32.72655972106742</v>
+        <v>189.814046382191</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>80.9990943388831</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>22.776546738526</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.17036643664921</v>
+        <v>35.18387422479719</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.90198946049134</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>15.83853571261379</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>10.40652566501619</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.269039928692631</v>
+        <v>5.89441321629785</v>
       </c>
       <c r="C2" t="n">
-        <v>4.186172210908399</v>
+        <v>4.58279828342411</v>
       </c>
       <c r="D2" t="n">
-        <v>23.26447534753666</v>
+        <v>24.67917378935632</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.256498192715675</v>
+        <v>4.844924920458009</v>
       </c>
       <c r="C3" t="n">
-        <v>5.787402716534947</v>
+        <v>7.112762117268142</v>
       </c>
       <c r="D3" t="n">
-        <v>14.34824269756713</v>
+        <v>9.807659565425636</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39864927875083</v>
+        <v>11.67879965945828</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14586975346022</v>
+        <v>59.95117158521919</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576311679853038</v>
+        <v>0.7785866439638857</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.068362486398782</v>
+        <v>2.657591035396115</v>
       </c>
       <c r="C2" t="n">
-        <v>4.201880174176349</v>
+        <v>7.445574589007809</v>
       </c>
       <c r="D2" t="n">
-        <v>19.79301546531994</v>
+        <v>24.78618428911922</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.19116306488765</v>
+        <v>14.62804079327748</v>
       </c>
       <c r="C3" t="n">
-        <v>12.49273953654066</v>
+        <v>14.30406405087603</v>
       </c>
       <c r="D3" t="n">
-        <v>30.41945261608742</v>
+        <v>29.05973204570559</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>9.750718198579321</v>
+        <v>6.164393834965722</v>
       </c>
       <c r="C4" t="n">
-        <v>9.508226515630358</v>
+        <v>12.13734686760332</v>
       </c>
       <c r="D4" t="n">
-        <v>22.59001467471911</v>
+        <v>19.37380919560656</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>21.07812321017901</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44332022721125</v>
+        <v>13.63133137147136</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1574707412838</v>
+        <v>73.76955801031559</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251225310991841</v>
+        <v>1.603686043702513</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.968625131193107</v>
+        <v>1.958586669972387</v>
       </c>
       <c r="C2" t="n">
-        <v>8.202502068982101</v>
+        <v>7.115707360380882</v>
       </c>
       <c r="D2" t="n">
-        <v>32.03835458039041</v>
+        <v>22.28861812951533</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.29915531235479</v>
+        <v>11.50608309377262</v>
       </c>
       <c r="C3" t="n">
-        <v>14.82929907264807</v>
+        <v>23.84174299763379</v>
       </c>
       <c r="D3" t="n">
-        <v>39.1962770920539</v>
+        <v>42.85819602889451</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.71840263979719</v>
+        <v>19.41209735607218</v>
       </c>
       <c r="C4" t="n">
-        <v>22.21989579021806</v>
+        <v>27.03144128873168</v>
       </c>
       <c r="D4" t="n">
-        <v>32.53217367562655</v>
+        <v>29.9158160438088</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.179341034707679</v>
+        <v>6.283185307179588</v>
       </c>
       <c r="C5" t="n">
-        <v>12.44365215132832</v>
+        <v>15.63433219013046</v>
       </c>
       <c r="D5" t="n">
-        <v>30.97414006898687</v>
+        <v>27.0716929446058</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.6242369756475</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.18437294641592</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74246559163759</v>
+        <v>14.84523177142079</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1290401089893</v>
+        <v>87.42192043170022</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022739677491275</v>
+        <v>2.474205295236799</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.711407232680442</v>
+        <v>2.147082229187774</v>
       </c>
       <c r="C2" t="n">
-        <v>7.712609964562943</v>
+        <v>8.684540191767285</v>
       </c>
       <c r="D2" t="n">
-        <v>26.30887497840602</v>
+        <v>22.14920995551229</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.79632056133118</v>
+        <v>8.816094384136358</v>
       </c>
       <c r="C3" t="n">
-        <v>24.81858196335937</v>
+        <v>26.23229865747478</v>
       </c>
       <c r="D3" t="n">
-        <v>54.82570054366313</v>
+        <v>50.7416300939964</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.95562573132642</v>
+        <v>21.33926809950867</v>
       </c>
       <c r="C4" t="n">
-        <v>30.69434197327653</v>
+        <v>46.59669128666636</v>
       </c>
       <c r="D4" t="n">
-        <v>43.87823189360694</v>
+        <v>44.36321525950487</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.61041039233004</v>
+        <v>18.33413837680919</v>
       </c>
       <c r="C5" t="n">
-        <v>28.17615911188346</v>
+        <v>35.53926689373454</v>
       </c>
       <c r="D5" t="n">
-        <v>35.78470381979624</v>
+        <v>32.07860623626453</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.217629195173304</v>
+        <v>6.722026530977913</v>
       </c>
       <c r="C6" t="n">
-        <v>16.1006623496477</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>38.56108632740622</v>
+        <v>33.93214590188251</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.79389940203295</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.95624762613216</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07572156093772</v>
+        <v>16.09437519082369</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9225644689747</v>
+        <v>101.6486854157286</v>
       </c>
       <c r="D21" t="n">
-        <v>6.885989166071512</v>
+        <v>3.388289513857619</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.418666490365646</v>
+        <v>1.508946221427348</v>
       </c>
       <c r="C2" t="n">
-        <v>14.80181013692916</v>
+        <v>8.342891990689393</v>
       </c>
       <c r="D2" t="n">
-        <v>27.42512211813465</v>
+        <v>30.61874740004952</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.30406405087603</v>
+        <v>8.025787482217675</v>
       </c>
       <c r="C3" t="n">
-        <v>26.1783025337412</v>
+        <v>30.62561963397925</v>
       </c>
       <c r="D3" t="n">
-        <v>58.91958847037233</v>
+        <v>56.28850462299088</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.16509784522949</v>
+        <v>19.18236839327843</v>
       </c>
       <c r="C4" t="n">
-        <v>40.73860273542564</v>
+        <v>57.44500341859361</v>
       </c>
       <c r="D4" t="n">
-        <v>52.48030527821749</v>
+        <v>58.55536007209676</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.30330328735004</v>
+        <v>25.54998400302325</v>
       </c>
       <c r="C5" t="n">
-        <v>32.34858685493241</v>
+        <v>63.00365892003907</v>
       </c>
       <c r="D5" t="n">
-        <v>35.31837366027901</v>
+        <v>40.79161711145498</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.861655689159212</v>
+        <v>15.73839744678062</v>
       </c>
       <c r="C6" t="n">
-        <v>21.25287430153496</v>
+        <v>38.88309957439917</v>
       </c>
       <c r="D6" t="n">
-        <v>31.63780151705772</v>
+        <v>36.34724525432967</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>7.425939634922873</v>
       </c>
       <c r="C7" t="n">
-        <v>14.31289978021425</v>
+        <v>22.57725195456389</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>25.03456645829366</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>38.2734342500619</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.068517113011851</v>
+        <v>17.37236500635195</v>
       </c>
       <c r="C21" t="n">
-        <v>67.15091257361259</v>
+        <v>115.5262272922404</v>
       </c>
       <c r="D21" t="n">
-        <v>5.301387834758889</v>
+        <v>4.343091251587987</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.683918296961532</v>
+        <v>1.993929587325272</v>
       </c>
       <c r="C2" t="n">
-        <v>9.69868557025424</v>
+        <v>7.666467822463342</v>
       </c>
       <c r="D2" t="n">
-        <v>24.38857646889926</v>
+        <v>25.7316073283089</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.5907754382451</v>
+        <v>6.474626109507715</v>
       </c>
       <c r="C3" t="n">
-        <v>46.93735774004001</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D3" t="n">
-        <v>68.25110039923827</v>
+        <v>66.35141859152068</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.04045694451915</v>
+        <v>17.30624853046277</v>
       </c>
       <c r="C4" t="n">
-        <v>56.6792402092811</v>
+        <v>67.74451858384691</v>
       </c>
       <c r="D4" t="n">
-        <v>72.14765703739384</v>
+        <v>71.38189382808135</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.15728492132452</v>
+        <v>27.19441140763665</v>
       </c>
       <c r="C5" t="n">
-        <v>59.02758071783948</v>
+        <v>85.38750657686634</v>
       </c>
       <c r="D5" t="n">
-        <v>47.46750150033328</v>
+        <v>51.95899724726245</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.75098024048658</v>
+        <v>24.95602664195392</v>
       </c>
       <c r="C6" t="n">
-        <v>39.28561613314037</v>
+        <v>68.99133816824036</v>
       </c>
       <c r="D6" t="n">
-        <v>35.90447703971436</v>
+        <v>40.45291415348983</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.102764713776425</v>
+        <v>12.81573453123786</v>
       </c>
       <c r="C7" t="n">
-        <v>23.95464398362217</v>
+        <v>39.46527596301753</v>
       </c>
       <c r="D7" t="n">
-        <v>33.95570784678443</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>19.3600647277471</v>
+        <v>27.95526587842792</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>39.22082078466007</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>39.160934174701</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>47.26722496866692</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.294577623113382</v>
+        <v>18.67149339431998</v>
       </c>
       <c r="C21" t="n">
-        <v>77.50488724557968</v>
+        <v>128.9222162941142</v>
       </c>
       <c r="D21" t="n">
-        <v>6.382755420224209</v>
+        <v>5.334712398377139</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.776202581160732</v>
+        <v>1.793653055658923</v>
       </c>
       <c r="C2" t="n">
-        <v>7.642905877561418</v>
+        <v>4.660356352059609</v>
       </c>
       <c r="D2" t="n">
-        <v>22.47122320250524</v>
+        <v>20.09441201052372</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.71072858461246</v>
+        <v>10.19054117008189</v>
       </c>
       <c r="C3" t="n">
-        <v>41.29721717914208</v>
+        <v>46.14214209960009</v>
       </c>
       <c r="D3" t="n">
-        <v>71.92283681312134</v>
+        <v>73.78815745119026</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.78742807873073</v>
+        <v>13.05626271877833</v>
       </c>
       <c r="C4" t="n">
-        <v>93.14233169271189</v>
+        <v>85.5357504802076</v>
       </c>
       <c r="D4" t="n">
-        <v>89.47943100816704</v>
+        <v>66.5448228892573</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.00497515844602</v>
+        <v>14.03899217072939</v>
       </c>
       <c r="C5" t="n">
-        <v>85.60839981032187</v>
+        <v>41.20885988575987</v>
       </c>
       <c r="D5" t="n">
-        <v>63.54362015737481</v>
+        <v>39.61351986635881</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.92835777978577</v>
+        <v>7.929576207201488</v>
       </c>
       <c r="C6" t="n">
-        <v>69.71586797397451</v>
+        <v>25.96231803880691</v>
       </c>
       <c r="D6" t="n">
-        <v>43.02902012943346</v>
+        <v>26.08307300642926</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.69029180927252</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>41.9206269713388</v>
+        <v>19.64280806657018</v>
       </c>
       <c r="D7" t="n">
-        <v>36.65060529494193</v>
+        <v>27.5478405811655</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>26.62008900065226</v>
+        <v>23.44904391593506</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>24.51718541815559</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>37.01188845010476</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
         <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.507788138967568</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>87.27803711549797</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.507788138967568</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
